--- a/src/assets/docs/Schedule.xlsx
+++ b/src/assets/docs/Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\workspace\nijisanji-schedule\src\assets\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0E0ECEF-7632-4CD5-8263-D8A07DF10951}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F170725-4F2F-4307-ACA8-64998383E37B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5217" uniqueCount="2945">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5213" uniqueCount="2945">
   <si>
     <t>id</t>
   </si>
@@ -9337,7 +9337,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F24484-CEFD-4B16-892C-5C7E8E706641}">
-  <dimension ref="A1:M1023"/>
+  <dimension ref="A1:M1021"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="33.140625" customWidth="1"/>
@@ -9401,7 +9401,7 @@
         <v>44713.583333333336</v>
       </c>
       <c r="L2" s="20">
-        <f t="shared" ref="L2:L12" si="0">(K2-DATE(1970,1,1))*86400*1000</f>
+        <f t="shared" ref="L2" si="0">(K2-DATE(1970,1,1))*86400*1000</f>
         <v>1654092000000.0002</v>
       </c>
     </row>
@@ -9474,126 +9474,102 @@
         <v>44714.5</v>
       </c>
       <c r="L7" s="20">
-        <f t="shared" ref="L7:L11" si="1">(K7-DATE(1970,1,1))*86400*1000</f>
+        <f t="shared" ref="L7:L9" si="1">(K7-DATE(1970,1,1))*86400*1000</f>
         <v>1654171200000</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="8">
-        <v>1819</v>
+        <v>1821</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>495</v>
+        <v>81</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>1716</v>
+        <v>1718</v>
       </c>
       <c r="D8" s="8" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="7">
-        <v>44715.25</v>
+        <v>44712.833333333336</v>
       </c>
       <c r="L8" s="20">
         <f t="shared" si="1"/>
-        <v>1654236000000</v>
+        <v>1654027200000.0002</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
-        <v>1820</v>
+        <v>1822</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>495</v>
+        <v>81</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>1717</v>
+        <v>1719</v>
       </c>
       <c r="D9" s="8" t="b">
         <v>1</v>
       </c>
       <c r="K9" s="7">
-        <v>44716.5</v>
+        <v>44713.958333333336</v>
       </c>
       <c r="L9" s="20">
         <f t="shared" si="1"/>
-        <v>1654344000000</v>
+        <v>1654124400000.0002</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="8">
-        <v>1821</v>
-      </c>
+      <c r="A10" s="8"/>
       <c r="B10" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>1718</v>
-      </c>
-      <c r="D10" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" s="7">
-        <v>44712.833333333336</v>
-      </c>
-      <c r="L10" s="20">
-        <f t="shared" si="1"/>
-        <v>1654027200000.0002</v>
+        <v>108</v>
+      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="8">
+        <v>1822</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="8">
-        <v>1822</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>1719</v>
-      </c>
-      <c r="D11" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="K11" s="7">
-        <v>44713.958333333336</v>
-      </c>
-      <c r="L11" s="20">
-        <f t="shared" si="1"/>
-        <v>1654124400000.0002</v>
-      </c>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="8"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="8"/>
-      <c r="B12" s="8" t="s">
-        <v>108</v>
-      </c>
+      <c r="B12" s="8"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="20"/>
-      <c r="M12" s="8">
-        <v>1822</v>
-      </c>
+      <c r="E12" s="8"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="8"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
+      <c r="E13" s="3"/>
       <c r="K13" s="4"/>
       <c r="L13" s="5"/>
-      <c r="M13" s="8"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
+      <c r="E14" s="3"/>
       <c r="K14" s="4"/>
       <c r="L14" s="5"/>
-      <c r="M14" s="8"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="8"/>
@@ -9637,6 +9613,7 @@
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="3"/>
+      <c r="I19" s="47"/>
       <c r="K19" s="4"/>
       <c r="L19" s="5"/>
     </row>
@@ -9646,6 +9623,7 @@
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
       <c r="E20" s="3"/>
+      <c r="I20" s="47"/>
       <c r="K20" s="4"/>
       <c r="L20" s="5"/>
     </row>
@@ -9714,7 +9692,7 @@
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
-      <c r="E27" s="3"/>
+      <c r="E27" s="8"/>
       <c r="I27" s="47"/>
       <c r="K27" s="4"/>
       <c r="L27" s="5"/>
@@ -9724,17 +9702,18 @@
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
-      <c r="E28" s="3"/>
+      <c r="E28" s="8"/>
       <c r="I28" s="47"/>
       <c r="K28" s="4"/>
       <c r="L28" s="5"/>
+      <c r="M28" s="8"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
+      <c r="E29" s="3"/>
       <c r="I29" s="47"/>
       <c r="K29" s="4"/>
       <c r="L29" s="5"/>
@@ -9744,11 +9723,10 @@
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
+      <c r="E30" s="3"/>
       <c r="I30" s="47"/>
       <c r="K30" s="4"/>
       <c r="L30" s="5"/>
-      <c r="M30" s="8"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" s="8"/>
@@ -9775,7 +9753,7 @@
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
-      <c r="E33" s="3"/>
+      <c r="E33" s="8"/>
       <c r="I33" s="47"/>
       <c r="K33" s="4"/>
       <c r="L33" s="5"/>
@@ -9785,30 +9763,20 @@
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
-      <c r="E34" s="3"/>
+      <c r="E34" s="8"/>
       <c r="I34" s="47"/>
       <c r="K34" s="4"/>
       <c r="L34" s="5"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A35" s="8"/>
       <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
       <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="I35" s="47"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="5"/>
+      <c r="M35" s="8"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A36" s="8"/>
       <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
       <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="I36" s="47"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="5"/>
+      <c r="M36" s="8"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B37" s="8"/>
@@ -9816,21 +9784,29 @@
       <c r="M37" s="8"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A38" s="8"/>
       <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
       <c r="D38" s="8"/>
-      <c r="M38" s="8"/>
+      <c r="H38" s="47"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="5"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A39" s="8"/>
       <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
       <c r="D39" s="8"/>
-      <c r="M39" s="8"/>
+      <c r="E39" s="3"/>
+      <c r="K39" s="4"/>
+      <c r="L39" s="5"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
-      <c r="H40" s="47"/>
+      <c r="E40" s="3"/>
       <c r="K40" s="4"/>
       <c r="L40" s="5"/>
     </row>
@@ -9839,7 +9815,7 @@
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
-      <c r="E41" s="3"/>
+      <c r="H41" s="47"/>
       <c r="K41" s="4"/>
       <c r="L41" s="5"/>
     </row>
@@ -9857,6 +9833,7 @@
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
+      <c r="E43" s="3"/>
       <c r="H43" s="47"/>
       <c r="K43" s="4"/>
       <c r="L43" s="5"/>
@@ -9876,7 +9853,6 @@
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
       <c r="E45" s="3"/>
-      <c r="H45" s="47"/>
       <c r="K45" s="4"/>
       <c r="L45" s="5"/>
     </row>
@@ -9886,6 +9862,7 @@
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
       <c r="E46" s="3"/>
+      <c r="I46" s="47"/>
       <c r="K46" s="4"/>
       <c r="L46" s="5"/>
     </row>
@@ -9904,18 +9881,15 @@
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
       <c r="E48" s="3"/>
-      <c r="I48" s="47"/>
       <c r="K48" s="4"/>
       <c r="L48" s="5"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="3"/>
       <c r="K49" s="4"/>
       <c r="L49" s="5"/>
+      <c r="M49" s="8"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A50" s="8"/>
@@ -9927,18 +9901,20 @@
       <c r="L50" s="5"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="3"/>
       <c r="K51" s="4"/>
       <c r="L51" s="5"/>
-      <c r="M51" s="8"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52" s="8"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
-      <c r="E52" s="3"/>
+      <c r="H52" s="47"/>
       <c r="K52" s="4"/>
       <c r="L52" s="5"/>
     </row>
@@ -9956,7 +9932,7 @@
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
       <c r="D54" s="8"/>
-      <c r="H54" s="47"/>
+      <c r="E54" s="3"/>
       <c r="K54" s="4"/>
       <c r="L54" s="5"/>
     </row>
@@ -9974,7 +9950,7 @@
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
       <c r="D56" s="8"/>
-      <c r="E56" s="3"/>
+      <c r="H56" s="47"/>
       <c r="K56" s="4"/>
       <c r="L56" s="5"/>
     </row>
@@ -9984,6 +9960,7 @@
       <c r="C57" s="8"/>
       <c r="D57" s="8"/>
       <c r="E57" s="3"/>
+      <c r="I57" s="47"/>
       <c r="K57" s="4"/>
       <c r="L57" s="5"/>
     </row>
@@ -9992,7 +9969,7 @@
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
       <c r="D58" s="8"/>
-      <c r="H58" s="47"/>
+      <c r="E58" s="3"/>
       <c r="K58" s="4"/>
       <c r="L58" s="5"/>
     </row>
@@ -10001,8 +9978,7 @@
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
       <c r="D59" s="8"/>
-      <c r="E59" s="3"/>
-      <c r="I59" s="47"/>
+      <c r="H59" s="47"/>
       <c r="K59" s="4"/>
       <c r="L59" s="5"/>
     </row>
@@ -10011,7 +9987,7 @@
       <c r="B60" s="8"/>
       <c r="C60" s="8"/>
       <c r="D60" s="8"/>
-      <c r="E60" s="3"/>
+      <c r="H60" s="47"/>
       <c r="K60" s="4"/>
       <c r="L60" s="5"/>
     </row>
@@ -10029,7 +10005,8 @@
       <c r="B62" s="8"/>
       <c r="C62" s="8"/>
       <c r="D62" s="8"/>
-      <c r="H62" s="47"/>
+      <c r="E62" s="3"/>
+      <c r="I62" s="47"/>
       <c r="K62" s="4"/>
       <c r="L62" s="5"/>
     </row>
@@ -10038,7 +10015,7 @@
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
       <c r="D63" s="8"/>
-      <c r="H63" s="47"/>
+      <c r="E63" s="3"/>
       <c r="K63" s="4"/>
       <c r="L63" s="5"/>
     </row>
@@ -10048,7 +10025,6 @@
       <c r="C64" s="8"/>
       <c r="D64" s="8"/>
       <c r="E64" s="3"/>
-      <c r="I64" s="47"/>
       <c r="K64" s="4"/>
       <c r="L64" s="5"/>
     </row>
@@ -10084,7 +10060,6 @@
       <c r="B68" s="8"/>
       <c r="C68" s="8"/>
       <c r="D68" s="8"/>
-      <c r="E68" s="3"/>
       <c r="K68" s="4"/>
       <c r="L68" s="5"/>
     </row>
@@ -10094,6 +10069,7 @@
       <c r="C69" s="8"/>
       <c r="D69" s="8"/>
       <c r="E69" s="3"/>
+      <c r="F69" s="47"/>
       <c r="K69" s="4"/>
       <c r="L69" s="5"/>
     </row>
@@ -10102,6 +10078,7 @@
       <c r="B70" s="8"/>
       <c r="C70" s="8"/>
       <c r="D70" s="8"/>
+      <c r="E70" s="3"/>
       <c r="K70" s="4"/>
       <c r="L70" s="5"/>
     </row>
@@ -10111,7 +10088,6 @@
       <c r="C71" s="8"/>
       <c r="D71" s="8"/>
       <c r="E71" s="3"/>
-      <c r="F71" s="47"/>
       <c r="K71" s="4"/>
       <c r="L71" s="5"/>
     </row>
@@ -10156,7 +10132,6 @@
       <c r="B76" s="8"/>
       <c r="C76" s="8"/>
       <c r="D76" s="8"/>
-      <c r="E76" s="3"/>
       <c r="K76" s="4"/>
       <c r="L76" s="5"/>
     </row>
@@ -10183,6 +10158,7 @@
       <c r="C79" s="8"/>
       <c r="D79" s="8"/>
       <c r="E79" s="3"/>
+      <c r="I79" s="47"/>
       <c r="K79" s="4"/>
       <c r="L79" s="5"/>
     </row>
@@ -10191,6 +10167,7 @@
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
       <c r="D80" s="8"/>
+      <c r="E80" s="3"/>
       <c r="K80" s="4"/>
       <c r="L80" s="5"/>
     </row>
@@ -10199,8 +10176,7 @@
       <c r="B81" s="8"/>
       <c r="C81" s="8"/>
       <c r="D81" s="8"/>
-      <c r="E81" s="3"/>
-      <c r="I81" s="47"/>
+      <c r="H81" s="47"/>
       <c r="K81" s="4"/>
       <c r="L81" s="5"/>
     </row>
@@ -10218,7 +10194,7 @@
       <c r="B83" s="8"/>
       <c r="C83" s="8"/>
       <c r="D83" s="8"/>
-      <c r="H83" s="47"/>
+      <c r="E83" s="3"/>
       <c r="K83" s="4"/>
       <c r="L83" s="5"/>
     </row>
@@ -10254,7 +10230,6 @@
       <c r="B87" s="8"/>
       <c r="C87" s="8"/>
       <c r="D87" s="8"/>
-      <c r="E87" s="3"/>
       <c r="K87" s="4"/>
       <c r="L87" s="5"/>
     </row>
@@ -10272,6 +10247,7 @@
       <c r="B89" s="8"/>
       <c r="C89" s="8"/>
       <c r="D89" s="8"/>
+      <c r="E89" s="3"/>
       <c r="K89" s="4"/>
       <c r="L89" s="5"/>
     </row>
@@ -10299,6 +10275,7 @@
       <c r="C92" s="8"/>
       <c r="D92" s="8"/>
       <c r="E92" s="3"/>
+      <c r="F92" s="47"/>
       <c r="K92" s="4"/>
       <c r="L92" s="5"/>
     </row>
@@ -10308,6 +10285,7 @@
       <c r="C93" s="8"/>
       <c r="D93" s="8"/>
       <c r="E93" s="3"/>
+      <c r="F93" s="47"/>
       <c r="K93" s="4"/>
       <c r="L93" s="5"/>
     </row>
@@ -10327,7 +10305,6 @@
       <c r="C95" s="8"/>
       <c r="D95" s="8"/>
       <c r="E95" s="3"/>
-      <c r="F95" s="47"/>
       <c r="K95" s="4"/>
       <c r="L95" s="5"/>
     </row>
@@ -10337,7 +10314,6 @@
       <c r="C96" s="8"/>
       <c r="D96" s="8"/>
       <c r="E96" s="3"/>
-      <c r="F96" s="47"/>
       <c r="K96" s="4"/>
       <c r="L96" s="5"/>
     </row>
@@ -10373,7 +10349,6 @@
       <c r="B100" s="8"/>
       <c r="C100" s="8"/>
       <c r="D100" s="8"/>
-      <c r="E100" s="3"/>
       <c r="K100" s="4"/>
       <c r="L100" s="5"/>
     </row>
@@ -10391,6 +10366,7 @@
       <c r="B102" s="8"/>
       <c r="C102" s="8"/>
       <c r="D102" s="8"/>
+      <c r="E102" s="3"/>
       <c r="K102" s="4"/>
       <c r="L102" s="5"/>
     </row>
@@ -10399,7 +10375,6 @@
       <c r="B103" s="8"/>
       <c r="C103" s="8"/>
       <c r="D103" s="8"/>
-      <c r="E103" s="3"/>
       <c r="K103" s="4"/>
       <c r="L103" s="5"/>
     </row>
@@ -10417,6 +10392,7 @@
       <c r="B105" s="8"/>
       <c r="C105" s="8"/>
       <c r="D105" s="8"/>
+      <c r="E105" s="3"/>
       <c r="K105" s="4"/>
       <c r="L105" s="5"/>
     </row>
@@ -10488,7 +10464,7 @@
       <c r="B113" s="8"/>
       <c r="C113" s="8"/>
       <c r="D113" s="8"/>
-      <c r="E113" s="3"/>
+      <c r="H113" s="47"/>
       <c r="K113" s="4"/>
       <c r="L113" s="5"/>
     </row>
@@ -10498,6 +10474,7 @@
       <c r="C114" s="8"/>
       <c r="D114" s="8"/>
       <c r="E114" s="3"/>
+      <c r="I114" s="47"/>
       <c r="K114" s="4"/>
       <c r="L114" s="5"/>
     </row>
@@ -10525,7 +10502,7 @@
       <c r="B117" s="8"/>
       <c r="C117" s="8"/>
       <c r="D117" s="8"/>
-      <c r="H117" s="47"/>
+      <c r="E117" s="3"/>
       <c r="K117" s="4"/>
       <c r="L117" s="5"/>
     </row>
@@ -10535,7 +10512,6 @@
       <c r="C118" s="8"/>
       <c r="D118" s="8"/>
       <c r="E118" s="3"/>
-      <c r="I118" s="47"/>
       <c r="K118" s="4"/>
       <c r="L118" s="5"/>
     </row>
@@ -10629,7 +10605,7 @@
       <c r="K128" s="4"/>
       <c r="L128" s="5"/>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A129" s="8"/>
       <c r="B129" s="8"/>
       <c r="C129" s="8"/>
@@ -10638,7 +10614,7 @@
       <c r="K129" s="4"/>
       <c r="L129" s="5"/>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A130" s="8"/>
       <c r="B130" s="8"/>
       <c r="C130" s="8"/>
@@ -10647,7 +10623,7 @@
       <c r="K130" s="4"/>
       <c r="L130" s="5"/>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A131" s="8"/>
       <c r="B131" s="8"/>
       <c r="C131" s="8"/>
@@ -10656,7 +10632,7 @@
       <c r="K131" s="4"/>
       <c r="L131" s="5"/>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A132" s="8"/>
       <c r="B132" s="8"/>
       <c r="C132" s="8"/>
@@ -10665,25 +10641,23 @@
       <c r="K132" s="4"/>
       <c r="L132" s="5"/>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A133" s="8"/>
       <c r="B133" s="8"/>
       <c r="C133" s="8"/>
       <c r="D133" s="8"/>
-      <c r="E133" s="3"/>
       <c r="K133" s="4"/>
       <c r="L133" s="5"/>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A134" s="8"/>
       <c r="B134" s="8"/>
       <c r="C134" s="8"/>
       <c r="D134" s="8"/>
-      <c r="E134" s="3"/>
       <c r="K134" s="4"/>
       <c r="L134" s="5"/>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A135" s="8"/>
       <c r="B135" s="8"/>
       <c r="C135" s="8"/>
@@ -10691,23 +10665,25 @@
       <c r="K135" s="4"/>
       <c r="L135" s="5"/>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A136" s="8"/>
       <c r="B136" s="8"/>
       <c r="C136" s="8"/>
       <c r="D136" s="8"/>
+      <c r="E136" s="3"/>
       <c r="K136" s="4"/>
       <c r="L136" s="5"/>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A137" s="8"/>
       <c r="B137" s="8"/>
       <c r="C137" s="8"/>
       <c r="D137" s="8"/>
+      <c r="E137" s="3"/>
       <c r="K137" s="4"/>
       <c r="L137" s="5"/>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A138" s="8"/>
       <c r="B138" s="8"/>
       <c r="C138" s="8"/>
@@ -10716,16 +10692,15 @@
       <c r="K138" s="4"/>
       <c r="L138" s="5"/>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A139" s="8"/>
       <c r="B139" s="8"/>
       <c r="C139" s="8"/>
       <c r="D139" s="8"/>
-      <c r="E139" s="3"/>
       <c r="K139" s="4"/>
       <c r="L139" s="5"/>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A140" s="8"/>
       <c r="B140" s="8"/>
       <c r="C140" s="8"/>
@@ -10734,64 +10709,65 @@
       <c r="K140" s="4"/>
       <c r="L140" s="5"/>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A141" s="8"/>
       <c r="B141" s="8"/>
       <c r="C141" s="8"/>
       <c r="D141" s="8"/>
+      <c r="E141" s="3"/>
       <c r="K141" s="4"/>
       <c r="L141" s="5"/>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A142" s="8"/>
       <c r="B142" s="8"/>
       <c r="C142" s="8"/>
       <c r="D142" s="8"/>
-      <c r="E142" s="3"/>
       <c r="K142" s="4"/>
       <c r="L142" s="5"/>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A143" s="8"/>
       <c r="B143" s="8"/>
       <c r="C143" s="8"/>
       <c r="D143" s="8"/>
-      <c r="E143" s="3"/>
       <c r="K143" s="4"/>
       <c r="L143" s="5"/>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A144" s="8"/>
-      <c r="B144" s="8"/>
-      <c r="C144" s="8"/>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A144" s="42"/>
+      <c r="B144" s="40"/>
+      <c r="C144" s="40"/>
       <c r="D144" s="8"/>
-      <c r="K144" s="4"/>
-      <c r="L144" s="5"/>
-    </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="E144" s="11"/>
+      <c r="F144" s="42"/>
+      <c r="G144" s="42"/>
+      <c r="H144" s="42"/>
+      <c r="I144" s="12"/>
+      <c r="J144" s="42"/>
+      <c r="K144" s="13"/>
+      <c r="L144" s="14"/>
+      <c r="M144" s="42"/>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A145" s="8"/>
       <c r="B145" s="8"/>
       <c r="C145" s="8"/>
       <c r="D145" s="8"/>
-      <c r="K145" s="4"/>
+      <c r="E145" s="3"/>
+      <c r="K145" s="15"/>
       <c r="L145" s="5"/>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A146" s="42"/>
-      <c r="B146" s="40"/>
-      <c r="C146" s="40"/>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A146" s="8"/>
+      <c r="B146" s="8"/>
+      <c r="C146" s="8"/>
       <c r="D146" s="8"/>
-      <c r="E146" s="11"/>
-      <c r="F146" s="42"/>
-      <c r="G146" s="42"/>
-      <c r="H146" s="42"/>
-      <c r="I146" s="12"/>
-      <c r="J146" s="42"/>
-      <c r="K146" s="13"/>
-      <c r="L146" s="14"/>
-      <c r="M146" s="42"/>
-    </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="E146" s="3"/>
+      <c r="K146" s="15"/>
+      <c r="L146" s="5"/>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A147" s="8"/>
       <c r="B147" s="8"/>
       <c r="C147" s="8"/>
@@ -10800,16 +10776,15 @@
       <c r="K147" s="15"/>
       <c r="L147" s="5"/>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A148" s="8"/>
       <c r="B148" s="8"/>
       <c r="C148" s="8"/>
       <c r="D148" s="8"/>
-      <c r="E148" s="3"/>
       <c r="K148" s="15"/>
       <c r="L148" s="5"/>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A149" s="8"/>
       <c r="B149" s="8"/>
       <c r="C149" s="8"/>
@@ -10818,24 +10793,24 @@
       <c r="K149" s="15"/>
       <c r="L149" s="5"/>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A150" s="8"/>
       <c r="B150" s="8"/>
       <c r="C150" s="8"/>
       <c r="D150" s="8"/>
+      <c r="E150" s="3"/>
       <c r="K150" s="15"/>
       <c r="L150" s="5"/>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A151" s="8"/>
       <c r="B151" s="8"/>
       <c r="C151" s="8"/>
       <c r="D151" s="8"/>
-      <c r="E151" s="3"/>
       <c r="K151" s="15"/>
       <c r="L151" s="5"/>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A152" s="8"/>
       <c r="B152" s="8"/>
       <c r="C152" s="8"/>
@@ -10844,24 +10819,24 @@
       <c r="K152" s="15"/>
       <c r="L152" s="5"/>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A153" s="8"/>
       <c r="B153" s="8"/>
       <c r="C153" s="8"/>
       <c r="D153" s="8"/>
+      <c r="E153" s="3"/>
       <c r="K153" s="15"/>
       <c r="L153" s="5"/>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A154" s="8"/>
       <c r="B154" s="8"/>
       <c r="C154" s="8"/>
       <c r="D154" s="8"/>
-      <c r="E154" s="3"/>
       <c r="K154" s="15"/>
       <c r="L154" s="5"/>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A155" s="8"/>
       <c r="B155" s="8"/>
       <c r="C155" s="8"/>
@@ -10870,24 +10845,24 @@
       <c r="K155" s="15"/>
       <c r="L155" s="5"/>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A156" s="8"/>
       <c r="B156" s="8"/>
       <c r="C156" s="8"/>
       <c r="D156" s="8"/>
+      <c r="E156" s="3"/>
       <c r="K156" s="15"/>
       <c r="L156" s="5"/>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A157" s="8"/>
       <c r="B157" s="8"/>
       <c r="C157" s="8"/>
       <c r="D157" s="8"/>
-      <c r="E157" s="3"/>
       <c r="K157" s="15"/>
       <c r="L157" s="5"/>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A158" s="8"/>
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
@@ -10896,7 +10871,7 @@
       <c r="K158" s="15"/>
       <c r="L158" s="5"/>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A159" s="8"/>
       <c r="B159" s="8"/>
       <c r="C159" s="8"/>
@@ -10904,7 +10879,7 @@
       <c r="K159" s="15"/>
       <c r="L159" s="5"/>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A160" s="8"/>
       <c r="B160" s="8"/>
       <c r="C160" s="8"/>
@@ -10918,6 +10893,7 @@
       <c r="B161" s="8"/>
       <c r="C161" s="8"/>
       <c r="D161" s="8"/>
+      <c r="E161" s="3"/>
       <c r="K161" s="15"/>
       <c r="L161" s="5"/>
     </row>
@@ -10971,7 +10947,6 @@
       <c r="B167" s="8"/>
       <c r="C167" s="8"/>
       <c r="D167" s="8"/>
-      <c r="E167" s="3"/>
       <c r="K167" s="15"/>
       <c r="L167" s="5"/>
     </row>
@@ -10989,6 +10964,7 @@
       <c r="B169" s="8"/>
       <c r="C169" s="8"/>
       <c r="D169" s="8"/>
+      <c r="E169" s="3"/>
       <c r="K169" s="15"/>
       <c r="L169" s="5"/>
     </row>
@@ -11015,7 +10991,7 @@
       <c r="B172" s="8"/>
       <c r="C172" s="8"/>
       <c r="D172" s="8"/>
-      <c r="E172" s="3"/>
+      <c r="H172" s="8"/>
       <c r="K172" s="15"/>
       <c r="L172" s="5"/>
     </row>
@@ -11033,7 +11009,7 @@
       <c r="B174" s="8"/>
       <c r="C174" s="8"/>
       <c r="D174" s="8"/>
-      <c r="H174" s="8"/>
+      <c r="E174" s="3"/>
       <c r="K174" s="15"/>
       <c r="L174" s="5"/>
     </row>
@@ -11132,7 +11108,7 @@
       <c r="B185" s="8"/>
       <c r="C185" s="8"/>
       <c r="D185" s="8"/>
-      <c r="E185" s="3"/>
+      <c r="E185" s="8"/>
       <c r="K185" s="15"/>
       <c r="L185" s="5"/>
     </row>
@@ -11141,7 +11117,8 @@
       <c r="B186" s="8"/>
       <c r="C186" s="8"/>
       <c r="D186" s="8"/>
-      <c r="E186" s="3"/>
+      <c r="E186" s="8"/>
+      <c r="H186" s="8"/>
       <c r="K186" s="15"/>
       <c r="L186" s="5"/>
     </row>
@@ -11150,7 +11127,7 @@
       <c r="B187" s="8"/>
       <c r="C187" s="8"/>
       <c r="D187" s="8"/>
-      <c r="E187" s="8"/>
+      <c r="E187" s="3"/>
       <c r="K187" s="15"/>
       <c r="L187" s="5"/>
     </row>
@@ -11159,8 +11136,7 @@
       <c r="B188" s="8"/>
       <c r="C188" s="8"/>
       <c r="D188" s="8"/>
-      <c r="E188" s="8"/>
-      <c r="H188" s="8"/>
+      <c r="E188" s="3"/>
       <c r="K188" s="15"/>
       <c r="L188" s="5"/>
     </row>
@@ -11187,7 +11163,7 @@
       <c r="B191" s="8"/>
       <c r="C191" s="8"/>
       <c r="D191" s="8"/>
-      <c r="E191" s="3"/>
+      <c r="E191" s="8"/>
       <c r="K191" s="15"/>
       <c r="L191" s="5"/>
     </row>
@@ -11205,7 +11181,7 @@
       <c r="B193" s="8"/>
       <c r="C193" s="8"/>
       <c r="D193" s="8"/>
-      <c r="E193" s="8"/>
+      <c r="E193" s="3"/>
       <c r="K193" s="15"/>
       <c r="L193" s="5"/>
     </row>
@@ -11223,7 +11199,7 @@
       <c r="B195" s="8"/>
       <c r="C195" s="8"/>
       <c r="D195" s="8"/>
-      <c r="E195" s="3"/>
+      <c r="E195" s="8"/>
       <c r="K195" s="15"/>
       <c r="L195" s="5"/>
     </row>
@@ -11277,7 +11253,7 @@
       <c r="B201" s="8"/>
       <c r="C201" s="8"/>
       <c r="D201" s="8"/>
-      <c r="E201" s="8"/>
+      <c r="E201" s="3"/>
       <c r="K201" s="15"/>
       <c r="L201" s="5"/>
     </row>
@@ -11296,6 +11272,7 @@
       <c r="C203" s="8"/>
       <c r="D203" s="8"/>
       <c r="E203" s="3"/>
+      <c r="G203" s="8"/>
       <c r="K203" s="15"/>
       <c r="L203" s="5"/>
     </row>
@@ -11314,7 +11291,6 @@
       <c r="C205" s="8"/>
       <c r="D205" s="8"/>
       <c r="E205" s="3"/>
-      <c r="G205" s="8"/>
       <c r="K205" s="15"/>
       <c r="L205" s="5"/>
     </row>
@@ -11323,7 +11299,7 @@
       <c r="B206" s="8"/>
       <c r="C206" s="8"/>
       <c r="D206" s="8"/>
-      <c r="E206" s="3"/>
+      <c r="E206" s="8"/>
       <c r="K206" s="15"/>
       <c r="L206" s="5"/>
     </row>
@@ -11341,7 +11317,7 @@
       <c r="B208" s="8"/>
       <c r="C208" s="8"/>
       <c r="D208" s="8"/>
-      <c r="E208" s="8"/>
+      <c r="E208" s="3"/>
       <c r="K208" s="15"/>
       <c r="L208" s="5"/>
     </row>
@@ -11351,6 +11327,8 @@
       <c r="C209" s="8"/>
       <c r="D209" s="8"/>
       <c r="E209" s="3"/>
+      <c r="G209" s="8"/>
+      <c r="H209" s="8"/>
       <c r="K209" s="15"/>
       <c r="L209" s="5"/>
     </row>
@@ -11368,9 +11346,7 @@
       <c r="B211" s="8"/>
       <c r="C211" s="8"/>
       <c r="D211" s="8"/>
-      <c r="E211" s="3"/>
-      <c r="G211" s="8"/>
-      <c r="H211" s="8"/>
+      <c r="E211" s="16"/>
       <c r="K211" s="15"/>
       <c r="L211" s="5"/>
     </row>
@@ -11388,7 +11364,7 @@
       <c r="B213" s="8"/>
       <c r="C213" s="8"/>
       <c r="D213" s="8"/>
-      <c r="E213" s="16"/>
+      <c r="E213" s="3"/>
       <c r="K213" s="15"/>
       <c r="L213" s="5"/>
     </row>
@@ -11425,6 +11401,7 @@
       <c r="C217" s="8"/>
       <c r="D217" s="8"/>
       <c r="E217" s="3"/>
+      <c r="G217" s="8"/>
       <c r="K217" s="15"/>
       <c r="L217" s="5"/>
     </row>
@@ -11433,7 +11410,8 @@
       <c r="B218" s="8"/>
       <c r="C218" s="8"/>
       <c r="D218" s="8"/>
-      <c r="E218" s="3"/>
+      <c r="E218" s="8"/>
+      <c r="G218" s="8"/>
       <c r="K218" s="15"/>
       <c r="L218" s="5"/>
     </row>
@@ -11443,7 +11421,6 @@
       <c r="C219" s="8"/>
       <c r="D219" s="8"/>
       <c r="E219" s="3"/>
-      <c r="G219" s="8"/>
       <c r="K219" s="15"/>
       <c r="L219" s="5"/>
     </row>
@@ -11453,7 +11430,6 @@
       <c r="C220" s="8"/>
       <c r="D220" s="8"/>
       <c r="E220" s="8"/>
-      <c r="G220" s="8"/>
       <c r="K220" s="15"/>
       <c r="L220" s="5"/>
     </row>
@@ -11471,7 +11447,7 @@
       <c r="B222" s="8"/>
       <c r="C222" s="8"/>
       <c r="D222" s="8"/>
-      <c r="E222" s="8"/>
+      <c r="E222" s="3"/>
       <c r="K222" s="15"/>
       <c r="L222" s="5"/>
     </row>
@@ -11480,7 +11456,7 @@
       <c r="B223" s="8"/>
       <c r="C223" s="8"/>
       <c r="D223" s="8"/>
-      <c r="E223" s="3"/>
+      <c r="E223" s="8"/>
       <c r="K223" s="15"/>
       <c r="L223" s="5"/>
     </row>
@@ -11489,7 +11465,7 @@
       <c r="B224" s="8"/>
       <c r="C224" s="8"/>
       <c r="D224" s="8"/>
-      <c r="E224" s="3"/>
+      <c r="E224" s="8"/>
       <c r="K224" s="15"/>
       <c r="L224" s="5"/>
     </row>
@@ -11498,7 +11474,7 @@
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
       <c r="D225" s="8"/>
-      <c r="E225" s="8"/>
+      <c r="E225" s="3"/>
       <c r="K225" s="15"/>
       <c r="L225" s="5"/>
     </row>
@@ -11525,7 +11501,7 @@
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
       <c r="D228" s="8"/>
-      <c r="E228" s="8"/>
+      <c r="E228" s="3"/>
       <c r="K228" s="15"/>
       <c r="L228" s="5"/>
     </row>
@@ -11552,7 +11528,7 @@
       <c r="B231" s="8"/>
       <c r="C231" s="8"/>
       <c r="D231" s="8"/>
-      <c r="E231" s="3"/>
+      <c r="E231" s="8"/>
       <c r="K231" s="15"/>
       <c r="L231" s="5"/>
     </row>
@@ -11570,7 +11546,7 @@
       <c r="B233" s="8"/>
       <c r="C233" s="8"/>
       <c r="D233" s="8"/>
-      <c r="E233" s="8"/>
+      <c r="E233" s="3"/>
       <c r="K233" s="15"/>
       <c r="L233" s="5"/>
     </row>
@@ -11580,7 +11556,7 @@
       <c r="C234" s="8"/>
       <c r="D234" s="8"/>
       <c r="E234" s="3"/>
-      <c r="K234" s="15"/>
+      <c r="K234" s="17"/>
       <c r="L234" s="5"/>
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.2">
@@ -11598,7 +11574,7 @@
       <c r="C236" s="8"/>
       <c r="D236" s="8"/>
       <c r="E236" s="3"/>
-      <c r="K236" s="17"/>
+      <c r="K236" s="15"/>
       <c r="L236" s="5"/>
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.2">
@@ -11624,7 +11600,6 @@
       <c r="B239" s="8"/>
       <c r="C239" s="8"/>
       <c r="D239" s="8"/>
-      <c r="E239" s="3"/>
       <c r="K239" s="15"/>
       <c r="L239" s="5"/>
     </row>
@@ -11642,6 +11617,7 @@
       <c r="B241" s="8"/>
       <c r="C241" s="8"/>
       <c r="D241" s="8"/>
+      <c r="E241" s="3"/>
       <c r="K241" s="15"/>
       <c r="L241" s="5"/>
     </row>
@@ -11659,16 +11635,15 @@
       <c r="B243" s="8"/>
       <c r="C243" s="8"/>
       <c r="D243" s="8"/>
-      <c r="E243" s="3"/>
       <c r="K243" s="15"/>
       <c r="L243" s="5"/>
+      <c r="M243" s="8"/>
     </row>
     <row r="244" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A244" s="8"/>
       <c r="B244" s="8"/>
       <c r="C244" s="8"/>
       <c r="D244" s="8"/>
-      <c r="E244" s="3"/>
       <c r="K244" s="15"/>
       <c r="L244" s="5"/>
     </row>
@@ -11677,15 +11652,17 @@
       <c r="B245" s="8"/>
       <c r="C245" s="8"/>
       <c r="D245" s="8"/>
+      <c r="E245" s="3"/>
       <c r="K245" s="15"/>
       <c r="L245" s="5"/>
-      <c r="M245" s="8"/>
     </row>
     <row r="246" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A246" s="8"/>
       <c r="B246" s="8"/>
       <c r="C246" s="8"/>
       <c r="D246" s="8"/>
+      <c r="E246" s="3"/>
+      <c r="G246" s="8"/>
       <c r="K246" s="15"/>
       <c r="L246" s="5"/>
     </row>
@@ -11704,7 +11681,6 @@
       <c r="C248" s="8"/>
       <c r="D248" s="8"/>
       <c r="E248" s="3"/>
-      <c r="G248" s="8"/>
       <c r="K248" s="15"/>
       <c r="L248" s="5"/>
     </row>
@@ -11740,7 +11716,7 @@
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
       <c r="D252" s="8"/>
-      <c r="E252" s="3"/>
+      <c r="G252" s="8"/>
       <c r="K252" s="15"/>
       <c r="L252" s="5"/>
     </row>
@@ -11758,7 +11734,6 @@
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
       <c r="D254" s="8"/>
-      <c r="G254" s="8"/>
       <c r="K254" s="15"/>
       <c r="L254" s="5"/>
     </row>
@@ -11793,6 +11768,7 @@
       <c r="B258" s="8"/>
       <c r="C258" s="8"/>
       <c r="D258" s="8"/>
+      <c r="E258" s="3"/>
       <c r="K258" s="15"/>
       <c r="L258" s="5"/>
     </row>
@@ -11846,7 +11822,7 @@
       <c r="B264" s="8"/>
       <c r="C264" s="8"/>
       <c r="D264" s="8"/>
-      <c r="E264" s="3"/>
+      <c r="G264" s="8"/>
       <c r="K264" s="15"/>
       <c r="L264" s="5"/>
     </row>
@@ -11864,7 +11840,7 @@
       <c r="B266" s="8"/>
       <c r="C266" s="8"/>
       <c r="D266" s="8"/>
-      <c r="G266" s="8"/>
+      <c r="E266" s="3"/>
       <c r="K266" s="15"/>
       <c r="L266" s="5"/>
     </row>
@@ -11950,24 +11926,24 @@
       <c r="L275" s="5"/>
     </row>
     <row r="276" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A276" s="8"/>
       <c r="B276" s="8"/>
       <c r="C276" s="8"/>
       <c r="D276" s="8"/>
-      <c r="E276" s="3"/>
       <c r="K276" s="15"/>
       <c r="L276" s="5"/>
+      <c r="M276" s="8"/>
     </row>
     <row r="277" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A277" s="8"/>
       <c r="B277" s="8"/>
       <c r="C277" s="8"/>
       <c r="D277" s="8"/>
-      <c r="E277" s="3"/>
       <c r="K277" s="15"/>
       <c r="L277" s="5"/>
+      <c r="M277" s="8"/>
     </row>
     <row r="278" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A278" s="8"/>
       <c r="B278" s="8"/>
       <c r="C278" s="8"/>
       <c r="D278" s="8"/>
@@ -11976,42 +11952,42 @@
       <c r="M278" s="8"/>
     </row>
     <row r="279" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A279" s="8"/>
-      <c r="B279" s="8"/>
-      <c r="C279" s="8"/>
-      <c r="D279" s="8"/>
-      <c r="K279" s="15"/>
-      <c r="L279" s="5"/>
-      <c r="M279" s="8"/>
+      <c r="A279" s="40"/>
+      <c r="B279" s="40"/>
+      <c r="C279" s="40"/>
+      <c r="D279" s="40"/>
+      <c r="E279" s="42"/>
+      <c r="F279" s="42"/>
+      <c r="G279" s="42"/>
+      <c r="H279" s="42"/>
+      <c r="I279" s="42"/>
+      <c r="J279" s="42"/>
+      <c r="K279" s="18"/>
+      <c r="L279" s="14"/>
+      <c r="M279" s="42"/>
     </row>
     <row r="280" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A280" s="8"/>
       <c r="B280" s="8"/>
       <c r="C280" s="8"/>
-      <c r="D280" s="8"/>
+      <c r="E280" s="3"/>
       <c r="K280" s="15"/>
       <c r="L280" s="5"/>
-      <c r="M280" s="8"/>
     </row>
     <row r="281" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A281" s="40"/>
-      <c r="B281" s="40"/>
-      <c r="C281" s="40"/>
-      <c r="D281" s="40"/>
-      <c r="E281" s="42"/>
-      <c r="F281" s="42"/>
-      <c r="G281" s="42"/>
-      <c r="H281" s="42"/>
-      <c r="I281" s="42"/>
-      <c r="J281" s="42"/>
-      <c r="K281" s="18"/>
-      <c r="L281" s="14"/>
-      <c r="M281" s="42"/>
+      <c r="A281" s="8"/>
+      <c r="B281" s="8"/>
+      <c r="C281" s="8"/>
+      <c r="D281" s="8"/>
+      <c r="E281" s="3"/>
+      <c r="K281" s="15"/>
+      <c r="L281" s="5"/>
     </row>
     <row r="282" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A282" s="8"/>
       <c r="B282" s="8"/>
       <c r="C282" s="8"/>
+      <c r="D282" s="8"/>
       <c r="E282" s="3"/>
       <c r="K282" s="15"/>
       <c r="L282" s="5"/>
@@ -12039,7 +12015,6 @@
       <c r="B285" s="8"/>
       <c r="C285" s="8"/>
       <c r="D285" s="8"/>
-      <c r="E285" s="3"/>
       <c r="K285" s="15"/>
       <c r="L285" s="5"/>
     </row>
@@ -12057,6 +12032,7 @@
       <c r="B287" s="8"/>
       <c r="C287" s="8"/>
       <c r="D287" s="8"/>
+      <c r="E287" s="3"/>
       <c r="K287" s="15"/>
       <c r="L287" s="5"/>
     </row>
@@ -12092,9 +12068,9 @@
       <c r="B291" s="8"/>
       <c r="C291" s="8"/>
       <c r="D291" s="8"/>
-      <c r="E291" s="3"/>
       <c r="K291" s="15"/>
       <c r="L291" s="5"/>
+      <c r="M291" s="8"/>
     </row>
     <row r="292" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A292" s="8"/>
@@ -12110,9 +12086,9 @@
       <c r="B293" s="8"/>
       <c r="C293" s="8"/>
       <c r="D293" s="8"/>
+      <c r="E293" s="3"/>
       <c r="K293" s="15"/>
       <c r="L293" s="5"/>
-      <c r="M293" s="8"/>
     </row>
     <row r="294" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A294" s="8"/>
@@ -12210,7 +12186,7 @@
       <c r="C304" s="8"/>
       <c r="D304" s="8"/>
       <c r="E304" s="3"/>
-      <c r="K304" s="15"/>
+      <c r="K304" s="4"/>
       <c r="L304" s="5"/>
     </row>
     <row r="305" spans="1:12" x14ac:dyDescent="0.2">
@@ -12228,7 +12204,7 @@
       <c r="C306" s="8"/>
       <c r="D306" s="8"/>
       <c r="E306" s="3"/>
-      <c r="K306" s="4"/>
+      <c r="K306" s="15"/>
       <c r="L306" s="5"/>
     </row>
     <row r="307" spans="1:12" x14ac:dyDescent="0.2">
@@ -12254,7 +12230,7 @@
       <c r="B309" s="8"/>
       <c r="C309" s="8"/>
       <c r="D309" s="8"/>
-      <c r="E309" s="3"/>
+      <c r="H309" s="8"/>
       <c r="K309" s="15"/>
       <c r="L309" s="5"/>
     </row>
@@ -12263,7 +12239,6 @@
       <c r="B310" s="8"/>
       <c r="C310" s="8"/>
       <c r="D310" s="8"/>
-      <c r="E310" s="3"/>
       <c r="K310" s="15"/>
       <c r="L310" s="5"/>
     </row>
@@ -12272,7 +12247,7 @@
       <c r="B311" s="8"/>
       <c r="C311" s="8"/>
       <c r="D311" s="8"/>
-      <c r="H311" s="8"/>
+      <c r="E311" s="3"/>
       <c r="K311" s="15"/>
       <c r="L311" s="5"/>
     </row>
@@ -12281,6 +12256,7 @@
       <c r="B312" s="8"/>
       <c r="C312" s="8"/>
       <c r="D312" s="8"/>
+      <c r="E312" s="3"/>
       <c r="K312" s="15"/>
       <c r="L312" s="5"/>
     </row>
@@ -12362,6 +12338,7 @@
       <c r="C321" s="8"/>
       <c r="D321" s="8"/>
       <c r="E321" s="3"/>
+      <c r="I321" s="8"/>
       <c r="K321" s="15"/>
       <c r="L321" s="5"/>
     </row>
@@ -12370,7 +12347,6 @@
       <c r="B322" s="8"/>
       <c r="C322" s="8"/>
       <c r="D322" s="8"/>
-      <c r="E322" s="3"/>
       <c r="K322" s="15"/>
       <c r="L322" s="5"/>
     </row>
@@ -12380,7 +12356,6 @@
       <c r="C323" s="8"/>
       <c r="D323" s="8"/>
       <c r="E323" s="3"/>
-      <c r="I323" s="8"/>
       <c r="K323" s="15"/>
       <c r="L323" s="5"/>
     </row>
@@ -12389,6 +12364,7 @@
       <c r="B324" s="8"/>
       <c r="C324" s="8"/>
       <c r="D324" s="8"/>
+      <c r="E324" s="3"/>
       <c r="K324" s="15"/>
       <c r="L324" s="5"/>
     </row>
@@ -12424,7 +12400,6 @@
       <c r="B328" s="8"/>
       <c r="C328" s="8"/>
       <c r="D328" s="8"/>
-      <c r="E328" s="3"/>
       <c r="K328" s="15"/>
       <c r="L328" s="5"/>
     </row>
@@ -12434,6 +12409,7 @@
       <c r="C329" s="8"/>
       <c r="D329" s="8"/>
       <c r="E329" s="3"/>
+      <c r="I329" s="8"/>
       <c r="K329" s="15"/>
       <c r="L329" s="5"/>
     </row>
@@ -12451,7 +12427,6 @@
       <c r="C331" s="8"/>
       <c r="D331" s="8"/>
       <c r="E331" s="3"/>
-      <c r="I331" s="8"/>
       <c r="K331" s="15"/>
       <c r="L331" s="5"/>
     </row>
@@ -12462,33 +12437,34 @@
       <c r="D332" s="8"/>
       <c r="K332" s="15"/>
       <c r="L332" s="5"/>
+      <c r="M332" s="8"/>
     </row>
     <row r="333" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A333" s="8"/>
       <c r="B333" s="8"/>
       <c r="C333" s="8"/>
       <c r="D333" s="8"/>
-      <c r="E333" s="3"/>
       <c r="K333" s="15"/>
       <c r="L333" s="5"/>
+      <c r="M333" s="8"/>
     </row>
     <row r="334" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A334" s="8"/>
       <c r="B334" s="8"/>
       <c r="C334" s="8"/>
       <c r="D334" s="8"/>
+      <c r="E334" s="3"/>
       <c r="K334" s="15"/>
       <c r="L334" s="5"/>
-      <c r="M334" s="8"/>
     </row>
     <row r="335" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A335" s="8"/>
       <c r="B335" s="8"/>
       <c r="C335" s="8"/>
       <c r="D335" s="8"/>
+      <c r="E335" s="3"/>
       <c r="K335" s="15"/>
       <c r="L335" s="5"/>
-      <c r="M335" s="8"/>
     </row>
     <row r="336" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A336" s="8"/>
@@ -12504,9 +12480,9 @@
       <c r="B337" s="8"/>
       <c r="C337" s="8"/>
       <c r="D337" s="8"/>
-      <c r="E337" s="3"/>
       <c r="K337" s="15"/>
       <c r="L337" s="5"/>
+      <c r="M337" s="8"/>
     </row>
     <row r="338" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A338" s="8"/>
@@ -12522,9 +12498,9 @@
       <c r="B339" s="8"/>
       <c r="C339" s="8"/>
       <c r="D339" s="8"/>
+      <c r="E339" s="3"/>
       <c r="K339" s="15"/>
       <c r="L339" s="5"/>
-      <c r="M339" s="8"/>
     </row>
     <row r="340" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A340" s="8"/>
@@ -12603,9 +12579,9 @@
       <c r="B348" s="8"/>
       <c r="C348" s="8"/>
       <c r="D348" s="8"/>
-      <c r="E348" s="3"/>
       <c r="K348" s="15"/>
       <c r="L348" s="5"/>
+      <c r="M348" s="8"/>
     </row>
     <row r="349" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A349" s="8"/>
@@ -12621,9 +12597,9 @@
       <c r="B350" s="8"/>
       <c r="C350" s="8"/>
       <c r="D350" s="8"/>
+      <c r="E350" s="3"/>
       <c r="K350" s="15"/>
       <c r="L350" s="5"/>
-      <c r="M350" s="8"/>
     </row>
     <row r="351" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A351" s="8"/>
@@ -12644,7 +12620,6 @@
       <c r="L352" s="5"/>
     </row>
     <row r="353" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A353" s="8"/>
       <c r="B353" s="8"/>
       <c r="C353" s="8"/>
       <c r="D353" s="8"/>
@@ -12662,6 +12637,7 @@
       <c r="L354" s="5"/>
     </row>
     <row r="355" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A355" s="8"/>
       <c r="B355" s="8"/>
       <c r="C355" s="8"/>
       <c r="D355" s="8"/>
@@ -12692,9 +12668,9 @@
       <c r="B358" s="8"/>
       <c r="C358" s="8"/>
       <c r="D358" s="8"/>
-      <c r="E358" s="3"/>
       <c r="K358" s="15"/>
       <c r="L358" s="5"/>
+      <c r="M358" s="8"/>
     </row>
     <row r="359" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A359" s="8"/>
@@ -12710,16 +12686,15 @@
       <c r="B360" s="8"/>
       <c r="C360" s="8"/>
       <c r="D360" s="8"/>
+      <c r="E360" s="3"/>
       <c r="K360" s="15"/>
       <c r="L360" s="5"/>
-      <c r="M360" s="8"/>
     </row>
     <row r="361" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A361" s="8"/>
       <c r="B361" s="8"/>
       <c r="C361" s="8"/>
       <c r="D361" s="8"/>
-      <c r="E361" s="3"/>
       <c r="K361" s="15"/>
       <c r="L361" s="5"/>
     </row>
@@ -12737,6 +12712,7 @@
       <c r="B363" s="8"/>
       <c r="C363" s="8"/>
       <c r="D363" s="8"/>
+      <c r="E363" s="3"/>
       <c r="K363" s="15"/>
       <c r="L363" s="5"/>
     </row>
@@ -12754,7 +12730,6 @@
       <c r="B365" s="8"/>
       <c r="C365" s="8"/>
       <c r="D365" s="8"/>
-      <c r="E365" s="3"/>
       <c r="K365" s="15"/>
       <c r="L365" s="5"/>
     </row>
@@ -12772,6 +12747,7 @@
       <c r="B367" s="8"/>
       <c r="C367" s="8"/>
       <c r="D367" s="8"/>
+      <c r="E367" s="3"/>
       <c r="K367" s="15"/>
       <c r="L367" s="5"/>
     </row>
@@ -12780,70 +12756,69 @@
       <c r="B368" s="8"/>
       <c r="C368" s="8"/>
       <c r="D368" s="8"/>
-      <c r="E368" s="3"/>
       <c r="K368" s="15"/>
       <c r="L368" s="5"/>
     </row>
     <row r="369" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A369" s="8"/>
       <c r="B369" s="8"/>
-      <c r="C369" s="8"/>
-      <c r="D369" s="8"/>
-      <c r="E369" s="3"/>
-      <c r="K369" s="15"/>
-      <c r="L369" s="5"/>
+      <c r="M369" s="8"/>
     </row>
     <row r="370" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A370" s="8"/>
       <c r="B370" s="8"/>
       <c r="C370" s="8"/>
       <c r="D370" s="8"/>
+      <c r="E370" s="16"/>
       <c r="K370" s="15"/>
       <c r="L370" s="5"/>
     </row>
     <row r="371" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A371" s="8"/>
       <c r="B371" s="8"/>
-      <c r="M371" s="8"/>
+      <c r="C371" s="8"/>
+      <c r="E371" s="3"/>
+      <c r="I371" s="8"/>
+      <c r="K371" s="15"/>
+      <c r="L371" s="5"/>
     </row>
     <row r="372" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A372" s="8"/>
       <c r="B372" s="8"/>
-      <c r="C372" s="8"/>
-      <c r="D372" s="8"/>
-      <c r="E372" s="16"/>
-      <c r="K372" s="15"/>
-      <c r="L372" s="5"/>
+      <c r="M372" s="8"/>
     </row>
     <row r="373" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A373" s="8"/>
       <c r="B373" s="8"/>
       <c r="C373" s="8"/>
-      <c r="E373" s="3"/>
+      <c r="E373" s="8"/>
       <c r="I373" s="8"/>
       <c r="K373" s="15"/>
       <c r="L373" s="5"/>
+      <c r="M373" s="8"/>
     </row>
     <row r="374" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B374" s="8"/>
+      <c r="C374" s="8"/>
+      <c r="E374" s="8"/>
+      <c r="I374" s="8"/>
+      <c r="K374" s="15"/>
+      <c r="L374" s="5"/>
       <c r="M374" s="8"/>
     </row>
     <row r="375" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A375" s="8"/>
       <c r="B375" s="8"/>
       <c r="C375" s="8"/>
-      <c r="E375" s="8"/>
-      <c r="I375" s="8"/>
+      <c r="D375" s="8"/>
+      <c r="E375" s="3"/>
       <c r="K375" s="15"/>
       <c r="L375" s="5"/>
-      <c r="M375" s="8"/>
     </row>
     <row r="376" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A376" s="8"/>
       <c r="B376" s="8"/>
       <c r="C376" s="8"/>
-      <c r="E376" s="8"/>
-      <c r="I376" s="8"/>
+      <c r="D376" s="8"/>
       <c r="K376" s="15"/>
       <c r="L376" s="5"/>
-      <c r="M376" s="8"/>
     </row>
     <row r="377" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A377" s="8"/>
@@ -12859,6 +12834,7 @@
       <c r="B378" s="8"/>
       <c r="C378" s="8"/>
       <c r="D378" s="8"/>
+      <c r="E378" s="3"/>
       <c r="K378" s="15"/>
       <c r="L378" s="5"/>
     </row>
@@ -12913,6 +12889,7 @@
       <c r="C384" s="8"/>
       <c r="D384" s="8"/>
       <c r="E384" s="3"/>
+      <c r="G384" s="8"/>
       <c r="K384" s="15"/>
       <c r="L384" s="5"/>
     </row>
@@ -12930,8 +12907,7 @@
       <c r="B386" s="8"/>
       <c r="C386" s="8"/>
       <c r="D386" s="8"/>
-      <c r="E386" s="3"/>
-      <c r="G386" s="8"/>
+      <c r="H386" s="8"/>
       <c r="K386" s="15"/>
       <c r="L386" s="5"/>
     </row>
@@ -12949,18 +12925,18 @@
       <c r="B388" s="8"/>
       <c r="C388" s="8"/>
       <c r="D388" s="8"/>
-      <c r="H388" s="8"/>
       <c r="K388" s="15"/>
       <c r="L388" s="5"/>
+      <c r="M388" s="8"/>
     </row>
     <row r="389" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A389" s="8"/>
       <c r="B389" s="8"/>
       <c r="C389" s="8"/>
       <c r="D389" s="8"/>
-      <c r="E389" s="3"/>
       <c r="K389" s="15"/>
       <c r="L389" s="5"/>
+      <c r="M389" s="8"/>
     </row>
     <row r="390" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A390" s="8"/>
@@ -12976,18 +12952,18 @@
       <c r="B391" s="8"/>
       <c r="C391" s="8"/>
       <c r="D391" s="8"/>
+      <c r="E391" s="3"/>
       <c r="K391" s="15"/>
       <c r="L391" s="5"/>
-      <c r="M391" s="8"/>
     </row>
     <row r="392" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A392" s="8"/>
       <c r="B392" s="8"/>
       <c r="C392" s="8"/>
       <c r="D392" s="8"/>
+      <c r="E392" s="3"/>
       <c r="K392" s="15"/>
       <c r="L392" s="5"/>
-      <c r="M392" s="8"/>
     </row>
     <row r="393" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A393" s="8"/>
@@ -13102,7 +13078,6 @@
       <c r="B405" s="8"/>
       <c r="C405" s="8"/>
       <c r="D405" s="8"/>
-      <c r="E405" s="3"/>
       <c r="K405" s="15"/>
       <c r="L405" s="5"/>
     </row>
@@ -13137,6 +13112,7 @@
       <c r="B409" s="8"/>
       <c r="C409" s="8"/>
       <c r="D409" s="8"/>
+      <c r="E409" s="3"/>
       <c r="K409" s="15"/>
       <c r="L409" s="5"/>
     </row>
@@ -13145,7 +13121,6 @@
       <c r="B410" s="8"/>
       <c r="C410" s="8"/>
       <c r="D410" s="8"/>
-      <c r="E410" s="3"/>
       <c r="K410" s="15"/>
       <c r="L410" s="5"/>
     </row>
@@ -13163,6 +13138,7 @@
       <c r="B412" s="8"/>
       <c r="C412" s="8"/>
       <c r="D412" s="8"/>
+      <c r="E412" s="3"/>
       <c r="K412" s="15"/>
       <c r="L412" s="5"/>
     </row>
@@ -13172,6 +13148,7 @@
       <c r="C413" s="8"/>
       <c r="D413" s="8"/>
       <c r="E413" s="3"/>
+      <c r="I413" s="8"/>
       <c r="K413" s="15"/>
       <c r="L413" s="5"/>
     </row>
@@ -13190,7 +13167,6 @@
       <c r="C415" s="8"/>
       <c r="D415" s="8"/>
       <c r="E415" s="3"/>
-      <c r="I415" s="8"/>
       <c r="K415" s="15"/>
       <c r="L415" s="5"/>
     </row>
@@ -13199,7 +13175,6 @@
       <c r="B416" s="8"/>
       <c r="C416" s="8"/>
       <c r="D416" s="8"/>
-      <c r="E416" s="3"/>
       <c r="K416" s="15"/>
       <c r="L416" s="5"/>
     </row>
@@ -13217,6 +13192,7 @@
       <c r="B418" s="8"/>
       <c r="C418" s="8"/>
       <c r="D418" s="8"/>
+      <c r="E418" s="3"/>
       <c r="K418" s="15"/>
       <c r="L418" s="5"/>
     </row>
@@ -13234,7 +13210,6 @@
       <c r="B420" s="8"/>
       <c r="C420" s="8"/>
       <c r="D420" s="8"/>
-      <c r="E420" s="3"/>
       <c r="K420" s="15"/>
       <c r="L420" s="5"/>
     </row>
@@ -13243,7 +13218,6 @@
       <c r="B421" s="8"/>
       <c r="C421" s="8"/>
       <c r="D421" s="8"/>
-      <c r="E421" s="3"/>
       <c r="K421" s="15"/>
       <c r="L421" s="5"/>
     </row>
@@ -13252,6 +13226,7 @@
       <c r="B422" s="8"/>
       <c r="C422" s="8"/>
       <c r="D422" s="8"/>
+      <c r="E422" s="3"/>
       <c r="K422" s="15"/>
       <c r="L422" s="5"/>
     </row>
@@ -13260,6 +13235,7 @@
       <c r="B423" s="8"/>
       <c r="C423" s="8"/>
       <c r="D423" s="8"/>
+      <c r="E423" s="3"/>
       <c r="K423" s="15"/>
       <c r="L423" s="5"/>
     </row>
@@ -13268,7 +13244,6 @@
       <c r="B424" s="8"/>
       <c r="C424" s="8"/>
       <c r="D424" s="8"/>
-      <c r="E424" s="3"/>
       <c r="K424" s="15"/>
       <c r="L424" s="5"/>
     </row>
@@ -13286,6 +13261,7 @@
       <c r="B426" s="8"/>
       <c r="C426" s="8"/>
       <c r="D426" s="8"/>
+      <c r="E426" s="3"/>
       <c r="K426" s="15"/>
       <c r="L426" s="5"/>
     </row>
@@ -13357,48 +13333,48 @@
       <c r="B434" s="8"/>
       <c r="C434" s="8"/>
       <c r="D434" s="8"/>
-      <c r="E434" s="3"/>
       <c r="K434" s="15"/>
       <c r="L434" s="5"/>
     </row>
     <row r="435" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A435" s="8"/>
-      <c r="B435" s="8"/>
-      <c r="C435" s="8"/>
-      <c r="D435" s="8"/>
-      <c r="E435" s="3"/>
-      <c r="K435" s="15"/>
-      <c r="L435" s="5"/>
+      <c r="A435" s="40"/>
+      <c r="B435" s="40"/>
+      <c r="C435" s="40"/>
+      <c r="D435" s="40"/>
+      <c r="E435" s="11"/>
+      <c r="F435" s="42"/>
+      <c r="G435" s="42"/>
+      <c r="H435" s="42"/>
+      <c r="I435" s="42"/>
+      <c r="J435" s="42"/>
+      <c r="K435" s="18"/>
+      <c r="L435" s="14"/>
+      <c r="M435" s="42"/>
     </row>
     <row r="436" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A436" s="8"/>
       <c r="B436" s="8"/>
       <c r="C436" s="8"/>
       <c r="D436" s="8"/>
+      <c r="E436" s="16"/>
       <c r="K436" s="15"/>
       <c r="L436" s="5"/>
     </row>
     <row r="437" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A437" s="40"/>
-      <c r="B437" s="40"/>
-      <c r="C437" s="40"/>
-      <c r="D437" s="40"/>
-      <c r="E437" s="11"/>
-      <c r="F437" s="42"/>
-      <c r="G437" s="42"/>
-      <c r="H437" s="42"/>
-      <c r="I437" s="42"/>
-      <c r="J437" s="42"/>
-      <c r="K437" s="18"/>
-      <c r="L437" s="14"/>
-      <c r="M437" s="42"/>
+      <c r="A437" s="8"/>
+      <c r="B437" s="8"/>
+      <c r="C437" s="8"/>
+      <c r="D437" s="8"/>
+      <c r="E437" s="3"/>
+      <c r="K437" s="15"/>
+      <c r="L437" s="5"/>
     </row>
     <row r="438" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A438" s="8"/>
       <c r="B438" s="8"/>
       <c r="C438" s="8"/>
       <c r="D438" s="8"/>
-      <c r="E438" s="16"/>
+      <c r="E438" s="3"/>
       <c r="K438" s="15"/>
       <c r="L438" s="5"/>
     </row>
@@ -13425,7 +13401,6 @@
       <c r="B441" s="8"/>
       <c r="C441" s="8"/>
       <c r="D441" s="8"/>
-      <c r="E441" s="3"/>
       <c r="K441" s="15"/>
       <c r="L441" s="5"/>
     </row>
@@ -13443,6 +13418,7 @@
       <c r="B443" s="8"/>
       <c r="C443" s="8"/>
       <c r="D443" s="8"/>
+      <c r="E443" s="3"/>
       <c r="K443" s="15"/>
       <c r="L443" s="5"/>
     </row>
@@ -13532,7 +13508,6 @@
       <c r="B453" s="8"/>
       <c r="C453" s="8"/>
       <c r="D453" s="8"/>
-      <c r="E453" s="3"/>
       <c r="K453" s="15"/>
       <c r="L453" s="5"/>
     </row>
@@ -13541,7 +13516,6 @@
       <c r="B454" s="8"/>
       <c r="C454" s="8"/>
       <c r="D454" s="8"/>
-      <c r="E454" s="3"/>
       <c r="K454" s="15"/>
       <c r="L454" s="5"/>
     </row>
@@ -13550,16 +13524,18 @@
       <c r="B455" s="8"/>
       <c r="C455" s="8"/>
       <c r="D455" s="8"/>
-      <c r="K455" s="15"/>
-      <c r="L455" s="5"/>
+      <c r="E455" s="3"/>
+      <c r="K455" s="21"/>
+      <c r="L455" s="20"/>
     </row>
     <row r="456" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A456" s="8"/>
       <c r="B456" s="8"/>
       <c r="C456" s="8"/>
       <c r="D456" s="8"/>
-      <c r="K456" s="15"/>
-      <c r="L456" s="5"/>
+      <c r="E456" s="3"/>
+      <c r="K456" s="21"/>
+      <c r="L456" s="20"/>
     </row>
     <row r="457" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A457" s="8"/>
@@ -13603,8 +13579,8 @@
       <c r="C461" s="8"/>
       <c r="D461" s="8"/>
       <c r="E461" s="3"/>
-      <c r="K461" s="21"/>
-      <c r="L461" s="20"/>
+      <c r="K461" s="15"/>
+      <c r="L461" s="5"/>
     </row>
     <row r="462" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A462" s="8"/>
@@ -13621,8 +13597,8 @@
       <c r="C463" s="8"/>
       <c r="D463" s="8"/>
       <c r="E463" s="3"/>
-      <c r="K463" s="15"/>
-      <c r="L463" s="5"/>
+      <c r="K463" s="21"/>
+      <c r="L463" s="20"/>
     </row>
     <row r="464" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A464" s="8"/>
@@ -13647,7 +13623,6 @@
       <c r="B466" s="8"/>
       <c r="C466" s="8"/>
       <c r="D466" s="8"/>
-      <c r="E466" s="3"/>
       <c r="K466" s="21"/>
       <c r="L466" s="20"/>
     </row>
@@ -13665,8 +13640,9 @@
       <c r="B468" s="8"/>
       <c r="C468" s="8"/>
       <c r="D468" s="8"/>
-      <c r="K468" s="21"/>
-      <c r="L468" s="20"/>
+      <c r="E468" s="3"/>
+      <c r="K468" s="15"/>
+      <c r="L468" s="5"/>
     </row>
     <row r="469" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A469" s="8"/>
@@ -13683,8 +13659,8 @@
       <c r="C470" s="8"/>
       <c r="D470" s="8"/>
       <c r="E470" s="3"/>
-      <c r="K470" s="15"/>
-      <c r="L470" s="5"/>
+      <c r="K470" s="21"/>
+      <c r="L470" s="20"/>
     </row>
     <row r="471" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A471" s="8"/>
@@ -13709,7 +13685,6 @@
       <c r="B473" s="8"/>
       <c r="C473" s="8"/>
       <c r="D473" s="8"/>
-      <c r="E473" s="3"/>
       <c r="K473" s="21"/>
       <c r="L473" s="20"/>
     </row>
@@ -13718,7 +13693,6 @@
       <c r="B474" s="8"/>
       <c r="C474" s="8"/>
       <c r="D474" s="8"/>
-      <c r="E474" s="3"/>
       <c r="K474" s="21"/>
       <c r="L474" s="20"/>
     </row>
@@ -13727,6 +13701,7 @@
       <c r="B475" s="8"/>
       <c r="C475" s="8"/>
       <c r="D475" s="8"/>
+      <c r="E475" s="3"/>
       <c r="K475" s="21"/>
       <c r="L475" s="20"/>
     </row>
@@ -13735,6 +13710,7 @@
       <c r="B476" s="8"/>
       <c r="C476" s="8"/>
       <c r="D476" s="8"/>
+      <c r="E476" s="3"/>
       <c r="K476" s="21"/>
       <c r="L476" s="20"/>
     </row>
@@ -13797,7 +13773,6 @@
       <c r="B483" s="8"/>
       <c r="C483" s="8"/>
       <c r="D483" s="8"/>
-      <c r="E483" s="3"/>
       <c r="K483" s="21"/>
       <c r="L483" s="20"/>
     </row>
@@ -13815,6 +13790,7 @@
       <c r="B485" s="8"/>
       <c r="C485" s="8"/>
       <c r="D485" s="8"/>
+      <c r="E485" s="3"/>
       <c r="K485" s="21"/>
       <c r="L485" s="20"/>
     </row>
@@ -13832,7 +13808,6 @@
       <c r="B487" s="8"/>
       <c r="C487" s="8"/>
       <c r="D487" s="8"/>
-      <c r="E487" s="3"/>
       <c r="K487" s="21"/>
       <c r="L487" s="20"/>
     </row>
@@ -13850,6 +13825,7 @@
       <c r="B489" s="8"/>
       <c r="C489" s="8"/>
       <c r="D489" s="8"/>
+      <c r="E489" s="3"/>
       <c r="K489" s="21"/>
       <c r="L489" s="20"/>
     </row>
@@ -13859,7 +13835,7 @@
       <c r="C490" s="8"/>
       <c r="D490" s="8"/>
       <c r="E490" s="3"/>
-      <c r="K490" s="21"/>
+      <c r="K490" s="22"/>
       <c r="L490" s="20"/>
     </row>
     <row r="491" spans="1:12" x14ac:dyDescent="0.2">
@@ -13877,7 +13853,7 @@
       <c r="C492" s="8"/>
       <c r="D492" s="8"/>
       <c r="E492" s="3"/>
-      <c r="K492" s="22"/>
+      <c r="K492" s="21"/>
       <c r="L492" s="20"/>
     </row>
     <row r="493" spans="1:12" x14ac:dyDescent="0.2">
@@ -13885,7 +13861,6 @@
       <c r="B493" s="8"/>
       <c r="C493" s="8"/>
       <c r="D493" s="8"/>
-      <c r="E493" s="3"/>
       <c r="K493" s="21"/>
       <c r="L493" s="20"/>
     </row>
@@ -13903,6 +13878,7 @@
       <c r="B495" s="8"/>
       <c r="C495" s="8"/>
       <c r="D495" s="8"/>
+      <c r="E495" s="3"/>
       <c r="K495" s="21"/>
       <c r="L495" s="20"/>
     </row>
@@ -13921,7 +13897,7 @@
       <c r="C497" s="8"/>
       <c r="D497" s="8"/>
       <c r="E497" s="3"/>
-      <c r="K497" s="21"/>
+      <c r="K497" s="22"/>
       <c r="L497" s="20"/>
     </row>
     <row r="498" spans="1:13" x14ac:dyDescent="0.2">
@@ -13938,8 +13914,7 @@
       <c r="B499" s="8"/>
       <c r="C499" s="8"/>
       <c r="D499" s="8"/>
-      <c r="E499" s="3"/>
-      <c r="K499" s="22"/>
+      <c r="K499" s="21"/>
       <c r="L499" s="20"/>
     </row>
     <row r="500" spans="1:13" x14ac:dyDescent="0.2">
@@ -13958,33 +13933,34 @@
       <c r="D501" s="8"/>
       <c r="K501" s="21"/>
       <c r="L501" s="20"/>
+      <c r="M501" s="8"/>
     </row>
     <row r="502" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A502" s="8"/>
       <c r="B502" s="8"/>
       <c r="C502" s="8"/>
       <c r="D502" s="8"/>
-      <c r="E502" s="3"/>
       <c r="K502" s="21"/>
       <c r="L502" s="20"/>
+      <c r="M502" s="8"/>
     </row>
     <row r="503" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A503" s="8"/>
       <c r="B503" s="8"/>
       <c r="C503" s="8"/>
       <c r="D503" s="8"/>
+      <c r="E503" s="3"/>
       <c r="K503" s="21"/>
       <c r="L503" s="20"/>
-      <c r="M503" s="8"/>
     </row>
     <row r="504" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A504" s="8"/>
       <c r="B504" s="8"/>
       <c r="C504" s="8"/>
       <c r="D504" s="8"/>
+      <c r="E504" s="3"/>
       <c r="K504" s="21"/>
       <c r="L504" s="20"/>
-      <c r="M504" s="8"/>
     </row>
     <row r="505" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A505" s="8"/>
@@ -14000,7 +13976,6 @@
       <c r="B506" s="8"/>
       <c r="C506" s="8"/>
       <c r="D506" s="8"/>
-      <c r="E506" s="3"/>
       <c r="K506" s="21"/>
       <c r="L506" s="20"/>
     </row>
@@ -14018,6 +13993,7 @@
       <c r="B508" s="8"/>
       <c r="C508" s="8"/>
       <c r="D508" s="8"/>
+      <c r="E508" s="3"/>
       <c r="K508" s="21"/>
       <c r="L508" s="20"/>
     </row>
@@ -14044,7 +14020,6 @@
       <c r="B511" s="8"/>
       <c r="C511" s="8"/>
       <c r="D511" s="8"/>
-      <c r="E511" s="3"/>
       <c r="K511" s="21"/>
       <c r="L511" s="20"/>
     </row>
@@ -14062,6 +14037,7 @@
       <c r="B513" s="8"/>
       <c r="C513" s="8"/>
       <c r="D513" s="8"/>
+      <c r="E513" s="3"/>
       <c r="K513" s="21"/>
       <c r="L513" s="20"/>
     </row>
@@ -14071,8 +14047,8 @@
       <c r="C514" s="8"/>
       <c r="D514" s="8"/>
       <c r="E514" s="3"/>
-      <c r="K514" s="21"/>
-      <c r="L514" s="20"/>
+      <c r="K514" s="15"/>
+      <c r="L514" s="5"/>
     </row>
     <row r="515" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A515" s="8"/>
@@ -14080,6 +14056,7 @@
       <c r="C515" s="8"/>
       <c r="D515" s="8"/>
       <c r="E515" s="3"/>
+      <c r="G515" s="8"/>
       <c r="K515" s="21"/>
       <c r="L515" s="20"/>
     </row>
@@ -14089,8 +14066,8 @@
       <c r="C516" s="8"/>
       <c r="D516" s="8"/>
       <c r="E516" s="3"/>
-      <c r="K516" s="15"/>
-      <c r="L516" s="5"/>
+      <c r="K516" s="21"/>
+      <c r="L516" s="20"/>
     </row>
     <row r="517" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A517" s="8"/>
@@ -14098,7 +14075,6 @@
       <c r="C517" s="8"/>
       <c r="D517" s="8"/>
       <c r="E517" s="3"/>
-      <c r="G517" s="8"/>
       <c r="K517" s="21"/>
       <c r="L517" s="20"/>
     </row>
@@ -14116,7 +14092,6 @@
       <c r="B519" s="8"/>
       <c r="C519" s="8"/>
       <c r="D519" s="8"/>
-      <c r="E519" s="3"/>
       <c r="K519" s="21"/>
       <c r="L519" s="20"/>
     </row>
@@ -14134,6 +14109,7 @@
       <c r="B521" s="8"/>
       <c r="C521" s="8"/>
       <c r="D521" s="8"/>
+      <c r="E521" s="3"/>
       <c r="K521" s="21"/>
       <c r="L521" s="20"/>
     </row>
@@ -14160,7 +14136,6 @@
       <c r="B524" s="8"/>
       <c r="C524" s="8"/>
       <c r="D524" s="8"/>
-      <c r="E524" s="3"/>
       <c r="K524" s="21"/>
       <c r="L524" s="20"/>
     </row>
@@ -14180,6 +14155,7 @@
       <c r="D526" s="8"/>
       <c r="K526" s="21"/>
       <c r="L526" s="20"/>
+      <c r="M526" s="8"/>
     </row>
     <row r="527" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A527" s="8"/>
@@ -14195,9 +14171,9 @@
       <c r="B528" s="8"/>
       <c r="C528" s="8"/>
       <c r="D528" s="8"/>
+      <c r="E528" s="3"/>
       <c r="K528" s="21"/>
       <c r="L528" s="20"/>
-      <c r="M528" s="8"/>
     </row>
     <row r="529" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A529" s="8"/>
@@ -14223,6 +14199,7 @@
       <c r="C531" s="8"/>
       <c r="D531" s="8"/>
       <c r="E531" s="3"/>
+      <c r="G531" s="8"/>
       <c r="K531" s="21"/>
       <c r="L531" s="20"/>
     </row>
@@ -14241,7 +14218,6 @@
       <c r="C533" s="8"/>
       <c r="D533" s="8"/>
       <c r="E533" s="3"/>
-      <c r="G533" s="8"/>
       <c r="K533" s="21"/>
       <c r="L533" s="20"/>
     </row>
@@ -14250,8 +14226,7 @@
       <c r="B534" s="8"/>
       <c r="C534" s="8"/>
       <c r="D534" s="8"/>
-      <c r="E534" s="3"/>
-      <c r="K534" s="21"/>
+      <c r="K534" s="7"/>
       <c r="L534" s="20"/>
     </row>
     <row r="535" spans="1:12" x14ac:dyDescent="0.2">
@@ -14259,7 +14234,6 @@
       <c r="B535" s="8"/>
       <c r="C535" s="8"/>
       <c r="D535" s="8"/>
-      <c r="E535" s="3"/>
       <c r="K535" s="21"/>
       <c r="L535" s="20"/>
     </row>
@@ -14268,7 +14242,8 @@
       <c r="B536" s="8"/>
       <c r="C536" s="8"/>
       <c r="D536" s="8"/>
-      <c r="K536" s="7"/>
+      <c r="E536" s="3"/>
+      <c r="K536" s="21"/>
       <c r="L536" s="20"/>
     </row>
     <row r="537" spans="1:12" x14ac:dyDescent="0.2">
@@ -14276,6 +14251,7 @@
       <c r="B537" s="8"/>
       <c r="C537" s="8"/>
       <c r="D537" s="8"/>
+      <c r="E537" s="3"/>
       <c r="K537" s="21"/>
       <c r="L537" s="20"/>
     </row>
@@ -14320,7 +14296,7 @@
       <c r="B542" s="8"/>
       <c r="C542" s="8"/>
       <c r="D542" s="8"/>
-      <c r="E542" s="3"/>
+      <c r="H542" s="8"/>
       <c r="K542" s="21"/>
       <c r="L542" s="20"/>
     </row>
@@ -14338,11 +14314,11 @@
       <c r="B544" s="8"/>
       <c r="C544" s="8"/>
       <c r="D544" s="8"/>
-      <c r="H544" s="8"/>
+      <c r="E544" s="3"/>
       <c r="K544" s="21"/>
       <c r="L544" s="20"/>
     </row>
-    <row r="545" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A545" s="8"/>
       <c r="B545" s="8"/>
       <c r="C545" s="8"/>
@@ -14351,7 +14327,7 @@
       <c r="K545" s="21"/>
       <c r="L545" s="20"/>
     </row>
-    <row r="546" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A546" s="8"/>
       <c r="B546" s="8"/>
       <c r="C546" s="8"/>
@@ -14360,7 +14336,7 @@
       <c r="K546" s="21"/>
       <c r="L546" s="20"/>
     </row>
-    <row r="547" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A547" s="8"/>
       <c r="B547" s="8"/>
       <c r="C547" s="8"/>
@@ -14369,7 +14345,7 @@
       <c r="K547" s="21"/>
       <c r="L547" s="20"/>
     </row>
-    <row r="548" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A548" s="8"/>
       <c r="B548" s="8"/>
       <c r="C548" s="8"/>
@@ -14378,7 +14354,7 @@
       <c r="K548" s="21"/>
       <c r="L548" s="20"/>
     </row>
-    <row r="549" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A549" s="8"/>
       <c r="B549" s="8"/>
       <c r="C549" s="8"/>
@@ -14387,7 +14363,7 @@
       <c r="K549" s="21"/>
       <c r="L549" s="20"/>
     </row>
-    <row r="550" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A550" s="8"/>
       <c r="B550" s="8"/>
       <c r="C550" s="8"/>
@@ -14396,7 +14372,7 @@
       <c r="K550" s="21"/>
       <c r="L550" s="20"/>
     </row>
-    <row r="551" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A551" s="8"/>
       <c r="B551" s="8"/>
       <c r="C551" s="8"/>
@@ -14405,16 +14381,15 @@
       <c r="K551" s="21"/>
       <c r="L551" s="20"/>
     </row>
-    <row r="552" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A552" s="8"/>
       <c r="B552" s="8"/>
       <c r="C552" s="8"/>
       <c r="D552" s="8"/>
-      <c r="E552" s="3"/>
       <c r="K552" s="21"/>
       <c r="L552" s="20"/>
     </row>
-    <row r="553" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A553" s="8"/>
       <c r="B553" s="8"/>
       <c r="C553" s="8"/>
@@ -14423,7 +14398,7 @@
       <c r="K553" s="21"/>
       <c r="L553" s="20"/>
     </row>
-    <row r="554" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A554" s="8"/>
       <c r="B554" s="8"/>
       <c r="C554" s="8"/>
@@ -14431,7 +14406,7 @@
       <c r="K554" s="21"/>
       <c r="L554" s="20"/>
     </row>
-    <row r="555" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A555" s="8"/>
       <c r="B555" s="8"/>
       <c r="C555" s="8"/>
@@ -14440,15 +14415,16 @@
       <c r="K555" s="21"/>
       <c r="L555" s="20"/>
     </row>
-    <row r="556" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A556" s="8"/>
       <c r="B556" s="8"/>
       <c r="C556" s="8"/>
       <c r="D556" s="8"/>
+      <c r="E556" s="3"/>
       <c r="K556" s="21"/>
       <c r="L556" s="20"/>
     </row>
-    <row r="557" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A557" s="8"/>
       <c r="B557" s="8"/>
       <c r="C557" s="8"/>
@@ -14457,7 +14433,7 @@
       <c r="K557" s="21"/>
       <c r="L557" s="20"/>
     </row>
-    <row r="558" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A558" s="8"/>
       <c r="B558" s="8"/>
       <c r="C558" s="8"/>
@@ -14466,7 +14442,7 @@
       <c r="K558" s="21"/>
       <c r="L558" s="20"/>
     </row>
-    <row r="559" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A559" s="8"/>
       <c r="B559" s="8"/>
       <c r="C559" s="8"/>
@@ -14475,14 +14451,20 @@
       <c r="K559" s="21"/>
       <c r="L559" s="20"/>
     </row>
-    <row r="560" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A560" s="8"/>
-      <c r="B560" s="8"/>
-      <c r="C560" s="8"/>
-      <c r="D560" s="8"/>
-      <c r="E560" s="3"/>
-      <c r="K560" s="21"/>
-      <c r="L560" s="20"/>
+    <row r="560" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A560" s="40"/>
+      <c r="B560" s="40"/>
+      <c r="C560" s="40"/>
+      <c r="D560" s="40"/>
+      <c r="E560" s="11"/>
+      <c r="F560" s="42"/>
+      <c r="G560" s="42"/>
+      <c r="H560" s="42"/>
+      <c r="I560" s="42"/>
+      <c r="J560" s="42"/>
+      <c r="K560" s="23"/>
+      <c r="L560" s="24"/>
+      <c r="M560" s="42"/>
     </row>
     <row r="561" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A561" s="8"/>
@@ -14494,28 +14476,22 @@
       <c r="L561" s="20"/>
     </row>
     <row r="562" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A562" s="40"/>
-      <c r="B562" s="40"/>
-      <c r="C562" s="40"/>
-      <c r="D562" s="40"/>
-      <c r="E562" s="11"/>
-      <c r="F562" s="42"/>
-      <c r="G562" s="42"/>
-      <c r="H562" s="42"/>
-      <c r="I562" s="42"/>
-      <c r="J562" s="42"/>
-      <c r="K562" s="23"/>
-      <c r="L562" s="24"/>
-      <c r="M562" s="42"/>
+      <c r="A562" s="8"/>
+      <c r="B562" s="8"/>
+      <c r="C562" s="8"/>
+      <c r="D562" s="8"/>
+      <c r="E562" s="3"/>
+      <c r="K562" s="21"/>
+      <c r="L562" s="20"/>
     </row>
     <row r="563" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A563" s="8"/>
       <c r="B563" s="8"/>
       <c r="C563" s="8"/>
       <c r="D563" s="8"/>
-      <c r="E563" s="3"/>
       <c r="K563" s="21"/>
       <c r="L563" s="20"/>
+      <c r="M563" s="8"/>
     </row>
     <row r="564" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A564" s="8"/>
@@ -14531,9 +14507,9 @@
       <c r="B565" s="8"/>
       <c r="C565" s="8"/>
       <c r="D565" s="8"/>
+      <c r="H565" s="8"/>
       <c r="K565" s="21"/>
       <c r="L565" s="20"/>
-      <c r="M565" s="8"/>
     </row>
     <row r="566" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A566" s="8"/>
@@ -14549,7 +14525,7 @@
       <c r="B567" s="8"/>
       <c r="C567" s="8"/>
       <c r="D567" s="8"/>
-      <c r="H567" s="8"/>
+      <c r="E567" s="3"/>
       <c r="K567" s="21"/>
       <c r="L567" s="20"/>
     </row>
@@ -14566,7 +14542,6 @@
       <c r="A569" s="8"/>
       <c r="B569" s="8"/>
       <c r="C569" s="8"/>
-      <c r="D569" s="8"/>
       <c r="E569" s="3"/>
       <c r="K569" s="21"/>
       <c r="L569" s="20"/>
@@ -14584,6 +14559,7 @@
       <c r="A571" s="8"/>
       <c r="B571" s="8"/>
       <c r="C571" s="8"/>
+      <c r="D571" s="8"/>
       <c r="E571" s="3"/>
       <c r="K571" s="21"/>
       <c r="L571" s="20"/>
@@ -14593,7 +14569,7 @@
       <c r="B572" s="8"/>
       <c r="C572" s="8"/>
       <c r="D572" s="8"/>
-      <c r="E572" s="3"/>
+      <c r="H572" s="8"/>
       <c r="K572" s="21"/>
       <c r="L572" s="20"/>
     </row>
@@ -14611,7 +14587,6 @@
       <c r="B574" s="8"/>
       <c r="C574" s="8"/>
       <c r="D574" s="8"/>
-      <c r="H574" s="8"/>
       <c r="K574" s="21"/>
       <c r="L574" s="20"/>
     </row>
@@ -14629,6 +14604,7 @@
       <c r="B576" s="8"/>
       <c r="C576" s="8"/>
       <c r="D576" s="8"/>
+      <c r="E576" s="3"/>
       <c r="K576" s="21"/>
       <c r="L576" s="20"/>
     </row>
@@ -14656,6 +14632,7 @@
       <c r="C579" s="8"/>
       <c r="D579" s="8"/>
       <c r="E579" s="3"/>
+      <c r="G579" s="8"/>
       <c r="K579" s="21"/>
       <c r="L579" s="20"/>
     </row>
@@ -14673,10 +14650,9 @@
       <c r="B581" s="8"/>
       <c r="C581" s="8"/>
       <c r="D581" s="8"/>
-      <c r="E581" s="3"/>
-      <c r="G581" s="8"/>
       <c r="K581" s="21"/>
       <c r="L581" s="20"/>
+      <c r="M581" s="8"/>
     </row>
     <row r="582" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A582" s="8"/>
@@ -14692,9 +14668,9 @@
       <c r="B583" s="8"/>
       <c r="C583" s="8"/>
       <c r="D583" s="8"/>
+      <c r="E583" s="3"/>
       <c r="K583" s="21"/>
       <c r="L583" s="20"/>
-      <c r="M583" s="8"/>
     </row>
     <row r="584" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A584" s="8"/>
@@ -14709,7 +14685,6 @@
       <c r="A585" s="8"/>
       <c r="B585" s="8"/>
       <c r="C585" s="8"/>
-      <c r="D585" s="8"/>
       <c r="E585" s="3"/>
       <c r="K585" s="21"/>
       <c r="L585" s="20"/>
@@ -14727,6 +14702,7 @@
       <c r="A587" s="8"/>
       <c r="B587" s="8"/>
       <c r="C587" s="8"/>
+      <c r="D587" s="8"/>
       <c r="E587" s="3"/>
       <c r="K587" s="21"/>
       <c r="L587" s="20"/>
@@ -14736,7 +14712,6 @@
       <c r="B588" s="8"/>
       <c r="C588" s="8"/>
       <c r="D588" s="8"/>
-      <c r="E588" s="3"/>
       <c r="K588" s="21"/>
       <c r="L588" s="20"/>
     </row>
@@ -14746,14 +14721,16 @@
       <c r="C589" s="8"/>
       <c r="D589" s="8"/>
       <c r="E589" s="3"/>
+      <c r="I589" s="8"/>
       <c r="K589" s="21"/>
-      <c r="L589" s="20"/>
+      <c r="L589" s="25"/>
     </row>
     <row r="590" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A590" s="8"/>
       <c r="B590" s="8"/>
       <c r="C590" s="8"/>
       <c r="D590" s="8"/>
+      <c r="E590" s="3"/>
       <c r="K590" s="21"/>
       <c r="L590" s="20"/>
     </row>
@@ -14762,10 +14739,8 @@
       <c r="B591" s="8"/>
       <c r="C591" s="8"/>
       <c r="D591" s="8"/>
-      <c r="E591" s="3"/>
-      <c r="I591" s="8"/>
       <c r="K591" s="21"/>
-      <c r="L591" s="25"/>
+      <c r="L591" s="20"/>
     </row>
     <row r="592" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A592" s="8"/>
@@ -14781,6 +14756,7 @@
       <c r="B593" s="8"/>
       <c r="C593" s="8"/>
       <c r="D593" s="8"/>
+      <c r="E593" s="3"/>
       <c r="K593" s="21"/>
       <c r="L593" s="20"/>
     </row>
@@ -14789,16 +14765,15 @@
       <c r="B594" s="8"/>
       <c r="C594" s="8"/>
       <c r="D594" s="8"/>
-      <c r="E594" s="3"/>
       <c r="K594" s="21"/>
       <c r="L594" s="20"/>
+      <c r="M594" s="8"/>
     </row>
     <row r="595" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A595" s="8"/>
       <c r="B595" s="8"/>
       <c r="C595" s="8"/>
       <c r="D595" s="8"/>
-      <c r="E595" s="3"/>
       <c r="K595" s="21"/>
       <c r="L595" s="20"/>
     </row>
@@ -14807,50 +14782,51 @@
       <c r="B596" s="8"/>
       <c r="C596" s="8"/>
       <c r="D596" s="8"/>
+      <c r="E596" s="3"/>
       <c r="K596" s="21"/>
       <c r="L596" s="20"/>
-      <c r="M596" s="8"/>
     </row>
     <row r="597" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A597" s="8"/>
       <c r="B597" s="8"/>
       <c r="C597" s="8"/>
       <c r="D597" s="8"/>
+      <c r="E597" s="3"/>
       <c r="K597" s="21"/>
       <c r="L597" s="20"/>
     </row>
     <row r="598" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A598" s="8"/>
       <c r="B598" s="8"/>
-      <c r="C598" s="8"/>
-      <c r="D598" s="8"/>
-      <c r="E598" s="3"/>
+      <c r="C598" s="26"/>
+      <c r="E598" s="27"/>
+      <c r="H598" s="8"/>
       <c r="K598" s="21"/>
-      <c r="L598" s="20"/>
+      <c r="L598" s="25"/>
     </row>
     <row r="599" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A599" s="8"/>
       <c r="B599" s="8"/>
       <c r="C599" s="8"/>
-      <c r="D599" s="8"/>
-      <c r="E599" s="3"/>
+      <c r="E599" s="16"/>
       <c r="K599" s="21"/>
       <c r="L599" s="20"/>
     </row>
     <row r="600" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A600" s="8"/>
       <c r="B600" s="8"/>
-      <c r="C600" s="26"/>
-      <c r="E600" s="27"/>
-      <c r="H600" s="8"/>
+      <c r="C600" s="8"/>
+      <c r="D600" s="8"/>
+      <c r="E600" s="3"/>
       <c r="K600" s="21"/>
-      <c r="L600" s="25"/>
+      <c r="L600" s="20"/>
     </row>
     <row r="601" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A601" s="8"/>
       <c r="B601" s="8"/>
       <c r="C601" s="8"/>
-      <c r="E601" s="16"/>
+      <c r="D601" s="8"/>
+      <c r="E601" s="3"/>
       <c r="K601" s="21"/>
       <c r="L601" s="20"/>
     </row>
@@ -14859,7 +14835,6 @@
       <c r="B602" s="8"/>
       <c r="C602" s="8"/>
       <c r="D602" s="8"/>
-      <c r="E602" s="3"/>
       <c r="K602" s="21"/>
       <c r="L602" s="20"/>
     </row>
@@ -14877,6 +14852,7 @@
       <c r="B604" s="8"/>
       <c r="C604" s="8"/>
       <c r="D604" s="8"/>
+      <c r="E604" s="3"/>
       <c r="K604" s="21"/>
       <c r="L604" s="20"/>
     </row>
@@ -14885,7 +14861,6 @@
       <c r="B605" s="8"/>
       <c r="C605" s="8"/>
       <c r="D605" s="8"/>
-      <c r="E605" s="3"/>
       <c r="K605" s="21"/>
       <c r="L605" s="20"/>
     </row>
@@ -14894,7 +14869,6 @@
       <c r="B606" s="8"/>
       <c r="C606" s="8"/>
       <c r="D606" s="8"/>
-      <c r="E606" s="3"/>
       <c r="K606" s="21"/>
       <c r="L606" s="20"/>
     </row>
@@ -14903,6 +14877,7 @@
       <c r="B607" s="8"/>
       <c r="C607" s="8"/>
       <c r="D607" s="8"/>
+      <c r="H607" s="8"/>
       <c r="K607" s="21"/>
       <c r="L607" s="20"/>
     </row>
@@ -14919,7 +14894,6 @@
       <c r="B609" s="8"/>
       <c r="C609" s="8"/>
       <c r="D609" s="8"/>
-      <c r="H609" s="8"/>
       <c r="K609" s="21"/>
       <c r="L609" s="20"/>
     </row>
@@ -14944,6 +14918,7 @@
       <c r="B612" s="8"/>
       <c r="C612" s="8"/>
       <c r="D612" s="8"/>
+      <c r="E612" s="3"/>
       <c r="K612" s="21"/>
       <c r="L612" s="20"/>
     </row>
@@ -14978,7 +14953,7 @@
       <c r="C616" s="8"/>
       <c r="D616" s="8"/>
       <c r="E616" s="3"/>
-      <c r="K616" s="21"/>
+      <c r="K616" s="7"/>
       <c r="L616" s="20"/>
     </row>
     <row r="617" spans="1:12" x14ac:dyDescent="0.2">
@@ -14986,6 +14961,7 @@
       <c r="B617" s="8"/>
       <c r="C617" s="8"/>
       <c r="D617" s="8"/>
+      <c r="E617" s="3"/>
       <c r="K617" s="21"/>
       <c r="L617" s="20"/>
     </row>
@@ -14995,7 +14971,7 @@
       <c r="C618" s="8"/>
       <c r="D618" s="8"/>
       <c r="E618" s="3"/>
-      <c r="K618" s="7"/>
+      <c r="K618" s="21"/>
       <c r="L618" s="20"/>
     </row>
     <row r="619" spans="1:12" x14ac:dyDescent="0.2">
@@ -15004,7 +14980,7 @@
       <c r="C619" s="8"/>
       <c r="D619" s="8"/>
       <c r="E619" s="3"/>
-      <c r="K619" s="21"/>
+      <c r="K619" s="7"/>
       <c r="L619" s="20"/>
     </row>
     <row r="620" spans="1:12" x14ac:dyDescent="0.2">
@@ -15022,7 +14998,7 @@
       <c r="C621" s="8"/>
       <c r="D621" s="8"/>
       <c r="E621" s="3"/>
-      <c r="K621" s="7"/>
+      <c r="K621" s="21"/>
       <c r="L621" s="20"/>
     </row>
     <row r="622" spans="1:12" x14ac:dyDescent="0.2">
@@ -15049,6 +15025,7 @@
       <c r="C624" s="8"/>
       <c r="D624" s="8"/>
       <c r="E624" s="3"/>
+      <c r="G624" s="8"/>
       <c r="K624" s="21"/>
       <c r="L624" s="20"/>
     </row>
@@ -15057,7 +15034,6 @@
       <c r="B625" s="8"/>
       <c r="C625" s="8"/>
       <c r="D625" s="8"/>
-      <c r="E625" s="3"/>
       <c r="K625" s="21"/>
       <c r="L625" s="20"/>
     </row>
@@ -15067,7 +15043,6 @@
       <c r="C626" s="8"/>
       <c r="D626" s="8"/>
       <c r="E626" s="3"/>
-      <c r="G626" s="8"/>
       <c r="K626" s="21"/>
       <c r="L626" s="20"/>
     </row>
@@ -15076,6 +15051,7 @@
       <c r="B627" s="8"/>
       <c r="C627" s="8"/>
       <c r="D627" s="8"/>
+      <c r="E627" s="3"/>
       <c r="K627" s="21"/>
       <c r="L627" s="20"/>
     </row>
@@ -15084,7 +15060,6 @@
       <c r="B628" s="8"/>
       <c r="C628" s="8"/>
       <c r="D628" s="8"/>
-      <c r="E628" s="3"/>
       <c r="K628" s="21"/>
       <c r="L628" s="20"/>
     </row>
@@ -15102,34 +15077,35 @@
       <c r="B630" s="8"/>
       <c r="C630" s="8"/>
       <c r="D630" s="8"/>
+      <c r="E630" s="3"/>
       <c r="K630" s="21"/>
       <c r="L630" s="20"/>
     </row>
     <row r="631" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A631" s="8"/>
       <c r="B631" s="8"/>
-      <c r="C631" s="8"/>
-      <c r="D631" s="8"/>
-      <c r="E631" s="3"/>
-      <c r="K631" s="21"/>
-      <c r="L631" s="20"/>
+      <c r="M631" s="8"/>
     </row>
     <row r="632" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A632" s="8"/>
       <c r="B632" s="8"/>
-      <c r="C632" s="8"/>
-      <c r="D632" s="8"/>
-      <c r="E632" s="3"/>
-      <c r="K632" s="21"/>
-      <c r="L632" s="20"/>
+      <c r="M632" s="8"/>
     </row>
     <row r="633" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A633" s="8"/>
       <c r="B633" s="8"/>
-      <c r="M633" s="8"/>
+      <c r="C633" s="8"/>
+      <c r="D633" s="8"/>
+      <c r="E633" s="3"/>
+      <c r="K633" s="21"/>
+      <c r="L633" s="20"/>
     </row>
     <row r="634" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A634" s="8"/>
       <c r="B634" s="8"/>
-      <c r="M634" s="8"/>
+      <c r="C634" s="8"/>
+      <c r="D634" s="8"/>
+      <c r="E634" s="3"/>
+      <c r="K634" s="21"/>
+      <c r="L634" s="20"/>
     </row>
     <row r="635" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A635" s="8"/>
@@ -15154,16 +15130,15 @@
       <c r="B637" s="8"/>
       <c r="C637" s="8"/>
       <c r="D637" s="8"/>
-      <c r="E637" s="3"/>
       <c r="K637" s="21"/>
       <c r="L637" s="20"/>
+      <c r="M637" s="8"/>
     </row>
     <row r="638" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A638" s="8"/>
       <c r="B638" s="8"/>
       <c r="C638" s="8"/>
       <c r="D638" s="8"/>
-      <c r="E638" s="3"/>
       <c r="K638" s="21"/>
       <c r="L638" s="20"/>
     </row>
@@ -15172,15 +15147,16 @@
       <c r="B639" s="8"/>
       <c r="C639" s="8"/>
       <c r="D639" s="8"/>
+      <c r="E639" s="3"/>
       <c r="K639" s="21"/>
       <c r="L639" s="20"/>
-      <c r="M639" s="8"/>
     </row>
     <row r="640" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A640" s="8"/>
       <c r="B640" s="8"/>
       <c r="C640" s="8"/>
       <c r="D640" s="8"/>
+      <c r="E640" s="3"/>
       <c r="K640" s="21"/>
       <c r="L640" s="20"/>
     </row>
@@ -15234,7 +15210,7 @@
       <c r="B646" s="8"/>
       <c r="C646" s="8"/>
       <c r="D646" s="8"/>
-      <c r="E646" s="3"/>
+      <c r="H646" s="8"/>
       <c r="K646" s="21"/>
       <c r="L646" s="20"/>
     </row>
@@ -15252,7 +15228,6 @@
       <c r="B648" s="8"/>
       <c r="C648" s="8"/>
       <c r="D648" s="8"/>
-      <c r="H648" s="8"/>
       <c r="K648" s="21"/>
       <c r="L648" s="20"/>
     </row>
@@ -15261,7 +15236,6 @@
       <c r="B649" s="8"/>
       <c r="C649" s="8"/>
       <c r="D649" s="8"/>
-      <c r="E649" s="3"/>
       <c r="K649" s="21"/>
       <c r="L649" s="20"/>
     </row>
@@ -15270,6 +15244,8 @@
       <c r="B650" s="8"/>
       <c r="C650" s="8"/>
       <c r="D650" s="8"/>
+      <c r="E650" s="3"/>
+      <c r="G650" s="8"/>
       <c r="K650" s="21"/>
       <c r="L650" s="20"/>
     </row>
@@ -15278,6 +15254,7 @@
       <c r="B651" s="8"/>
       <c r="C651" s="8"/>
       <c r="D651" s="8"/>
+      <c r="E651" s="3"/>
       <c r="K651" s="21"/>
       <c r="L651" s="20"/>
     </row>
@@ -15287,7 +15264,6 @@
       <c r="C652" s="8"/>
       <c r="D652" s="8"/>
       <c r="E652" s="3"/>
-      <c r="G652" s="8"/>
       <c r="K652" s="21"/>
       <c r="L652" s="20"/>
     </row>
@@ -15332,7 +15308,6 @@
       <c r="B657" s="8"/>
       <c r="C657" s="8"/>
       <c r="D657" s="8"/>
-      <c r="E657" s="3"/>
       <c r="K657" s="21"/>
       <c r="L657" s="20"/>
     </row>
@@ -15350,6 +15325,7 @@
       <c r="B659" s="8"/>
       <c r="C659" s="8"/>
       <c r="D659" s="8"/>
+      <c r="E659" s="3"/>
       <c r="K659" s="21"/>
       <c r="L659" s="20"/>
     </row>
@@ -15430,7 +15406,6 @@
       <c r="B668" s="8"/>
       <c r="C668" s="8"/>
       <c r="D668" s="8"/>
-      <c r="E668" s="3"/>
       <c r="K668" s="21"/>
       <c r="L668" s="20"/>
     </row>
@@ -15439,7 +15414,6 @@
       <c r="B669" s="8"/>
       <c r="C669" s="8"/>
       <c r="D669" s="8"/>
-      <c r="E669" s="3"/>
       <c r="K669" s="21"/>
       <c r="L669" s="20"/>
     </row>
@@ -15448,6 +15422,7 @@
       <c r="B670" s="8"/>
       <c r="C670" s="8"/>
       <c r="D670" s="8"/>
+      <c r="E670" s="3"/>
       <c r="K670" s="21"/>
       <c r="L670" s="20"/>
     </row>
@@ -15456,6 +15431,7 @@
       <c r="B671" s="8"/>
       <c r="C671" s="8"/>
       <c r="D671" s="8"/>
+      <c r="E671" s="3"/>
       <c r="K671" s="21"/>
       <c r="L671" s="20"/>
     </row>
@@ -15464,7 +15440,6 @@
       <c r="B672" s="8"/>
       <c r="C672" s="8"/>
       <c r="D672" s="8"/>
-      <c r="E672" s="3"/>
       <c r="K672" s="21"/>
       <c r="L672" s="20"/>
     </row>
@@ -15482,6 +15457,7 @@
       <c r="B674" s="8"/>
       <c r="C674" s="8"/>
       <c r="D674" s="8"/>
+      <c r="E674" s="3"/>
       <c r="K674" s="21"/>
       <c r="L674" s="20"/>
     </row>
@@ -15490,7 +15466,6 @@
       <c r="B675" s="8"/>
       <c r="C675" s="8"/>
       <c r="D675" s="8"/>
-      <c r="E675" s="3"/>
       <c r="K675" s="21"/>
       <c r="L675" s="20"/>
     </row>
@@ -15508,6 +15483,7 @@
       <c r="B677" s="8"/>
       <c r="C677" s="8"/>
       <c r="D677" s="8"/>
+      <c r="E677" s="3"/>
       <c r="K677" s="21"/>
       <c r="L677" s="20"/>
     </row>
@@ -15516,7 +15492,6 @@
       <c r="B678" s="8"/>
       <c r="C678" s="8"/>
       <c r="D678" s="8"/>
-      <c r="E678" s="3"/>
       <c r="K678" s="21"/>
       <c r="L678" s="20"/>
     </row>
@@ -15534,6 +15509,7 @@
       <c r="B680" s="8"/>
       <c r="C680" s="8"/>
       <c r="D680" s="8"/>
+      <c r="E680" s="3"/>
       <c r="K680" s="21"/>
       <c r="L680" s="20"/>
     </row>
@@ -15556,13 +15532,19 @@
       <c r="L682" s="20"/>
     </row>
     <row r="683" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A683" s="8"/>
-      <c r="B683" s="8"/>
-      <c r="C683" s="8"/>
-      <c r="D683" s="8"/>
-      <c r="E683" s="3"/>
-      <c r="K683" s="21"/>
-      <c r="L683" s="20"/>
+      <c r="A683" s="40"/>
+      <c r="B683" s="40"/>
+      <c r="C683" s="40"/>
+      <c r="D683" s="40"/>
+      <c r="E683" s="11"/>
+      <c r="F683" s="42"/>
+      <c r="G683" s="42"/>
+      <c r="H683" s="42"/>
+      <c r="I683" s="42"/>
+      <c r="J683" s="42"/>
+      <c r="K683" s="23"/>
+      <c r="L683" s="24"/>
+      <c r="M683" s="42"/>
     </row>
     <row r="684" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A684" s="8"/>
@@ -15574,19 +15556,13 @@
       <c r="L684" s="20"/>
     </row>
     <row r="685" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A685" s="40"/>
-      <c r="B685" s="40"/>
-      <c r="C685" s="40"/>
-      <c r="D685" s="40"/>
-      <c r="E685" s="11"/>
-      <c r="F685" s="42"/>
-      <c r="G685" s="42"/>
-      <c r="H685" s="42"/>
-      <c r="I685" s="42"/>
-      <c r="J685" s="42"/>
-      <c r="K685" s="23"/>
-      <c r="L685" s="24"/>
-      <c r="M685" s="42"/>
+      <c r="A685" s="8"/>
+      <c r="B685" s="8"/>
+      <c r="C685" s="8"/>
+      <c r="D685" s="8"/>
+      <c r="E685" s="3"/>
+      <c r="K685" s="21"/>
+      <c r="L685" s="20"/>
     </row>
     <row r="686" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A686" s="8"/>
@@ -15611,9 +15587,9 @@
       <c r="B688" s="8"/>
       <c r="C688" s="8"/>
       <c r="D688" s="8"/>
-      <c r="E688" s="3"/>
       <c r="K688" s="21"/>
       <c r="L688" s="20"/>
+      <c r="M688" s="8"/>
     </row>
     <row r="689" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A689" s="8"/>
@@ -15629,9 +15605,9 @@
       <c r="B690" s="8"/>
       <c r="C690" s="8"/>
       <c r="D690" s="8"/>
+      <c r="E690" s="3"/>
       <c r="K690" s="21"/>
       <c r="L690" s="20"/>
-      <c r="M690" s="8"/>
     </row>
     <row r="691" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A691" s="8"/>
@@ -15647,7 +15623,6 @@
       <c r="B692" s="8"/>
       <c r="C692" s="8"/>
       <c r="D692" s="8"/>
-      <c r="E692" s="3"/>
       <c r="K692" s="21"/>
       <c r="L692" s="20"/>
     </row>
@@ -15665,6 +15640,7 @@
       <c r="B694" s="8"/>
       <c r="C694" s="8"/>
       <c r="D694" s="8"/>
+      <c r="E694" s="3"/>
       <c r="K694" s="21"/>
       <c r="L694" s="20"/>
     </row>
@@ -15683,6 +15659,7 @@
       <c r="C696" s="8"/>
       <c r="D696" s="8"/>
       <c r="E696" s="3"/>
+      <c r="G696" s="8"/>
       <c r="K696" s="21"/>
       <c r="L696" s="20"/>
     </row>
@@ -15691,9 +15668,9 @@
       <c r="B697" s="8"/>
       <c r="C697" s="8"/>
       <c r="D697" s="8"/>
-      <c r="E697" s="3"/>
       <c r="K697" s="21"/>
       <c r="L697" s="20"/>
+      <c r="M697" s="8"/>
     </row>
     <row r="698" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A698" s="8"/>
@@ -15701,7 +15678,6 @@
       <c r="C698" s="8"/>
       <c r="D698" s="8"/>
       <c r="E698" s="3"/>
-      <c r="G698" s="8"/>
       <c r="K698" s="21"/>
       <c r="L698" s="20"/>
     </row>
@@ -15710,16 +15686,15 @@
       <c r="B699" s="8"/>
       <c r="C699" s="8"/>
       <c r="D699" s="8"/>
+      <c r="E699" s="3"/>
       <c r="K699" s="21"/>
       <c r="L699" s="20"/>
-      <c r="M699" s="8"/>
     </row>
     <row r="700" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A700" s="8"/>
       <c r="B700" s="8"/>
       <c r="C700" s="8"/>
       <c r="D700" s="8"/>
-      <c r="E700" s="3"/>
       <c r="K700" s="21"/>
       <c r="L700" s="20"/>
     </row>
@@ -15729,7 +15704,7 @@
       <c r="C701" s="8"/>
       <c r="D701" s="8"/>
       <c r="E701" s="3"/>
-      <c r="K701" s="21"/>
+      <c r="K701" s="7"/>
       <c r="L701" s="20"/>
     </row>
     <row r="702" spans="1:13" x14ac:dyDescent="0.2">
@@ -15737,6 +15712,7 @@
       <c r="B702" s="8"/>
       <c r="C702" s="8"/>
       <c r="D702" s="8"/>
+      <c r="E702" s="3"/>
       <c r="K702" s="21"/>
       <c r="L702" s="20"/>
     </row>
@@ -15746,7 +15722,7 @@
       <c r="C703" s="8"/>
       <c r="D703" s="8"/>
       <c r="E703" s="3"/>
-      <c r="K703" s="7"/>
+      <c r="K703" s="21"/>
       <c r="L703" s="20"/>
     </row>
     <row r="704" spans="1:13" x14ac:dyDescent="0.2">
@@ -15758,7 +15734,7 @@
       <c r="K704" s="21"/>
       <c r="L704" s="20"/>
     </row>
-    <row r="705" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A705" s="8"/>
       <c r="B705" s="8"/>
       <c r="C705" s="8"/>
@@ -15767,7 +15743,7 @@
       <c r="K705" s="21"/>
       <c r="L705" s="20"/>
     </row>
-    <row r="706" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A706" s="8"/>
       <c r="B706" s="8"/>
       <c r="C706" s="8"/>
@@ -15776,7 +15752,7 @@
       <c r="K706" s="21"/>
       <c r="L706" s="20"/>
     </row>
-    <row r="707" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A707" s="8"/>
       <c r="B707" s="8"/>
       <c r="C707" s="8"/>
@@ -15785,25 +15761,23 @@
       <c r="K707" s="21"/>
       <c r="L707" s="20"/>
     </row>
-    <row r="708" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A708" s="8"/>
       <c r="B708" s="8"/>
       <c r="C708" s="8"/>
-      <c r="D708" s="8"/>
       <c r="E708" s="3"/>
       <c r="K708" s="21"/>
       <c r="L708" s="20"/>
     </row>
-    <row r="709" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A709" s="8"/>
       <c r="B709" s="8"/>
       <c r="C709" s="8"/>
-      <c r="D709" s="8"/>
       <c r="E709" s="3"/>
       <c r="K709" s="21"/>
       <c r="L709" s="20"/>
     </row>
-    <row r="710" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A710" s="8"/>
       <c r="B710" s="8"/>
       <c r="C710" s="8"/>
@@ -15811,32 +15785,33 @@
       <c r="K710" s="21"/>
       <c r="L710" s="20"/>
     </row>
-    <row r="711" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A711" s="8"/>
       <c r="B711" s="8"/>
       <c r="C711" s="8"/>
+      <c r="D711" s="8"/>
       <c r="E711" s="3"/>
       <c r="K711" s="21"/>
       <c r="L711" s="20"/>
     </row>
-    <row r="712" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A712" s="8"/>
       <c r="B712" s="8"/>
       <c r="C712" s="8"/>
+      <c r="D712" s="8"/>
       <c r="E712" s="3"/>
       <c r="K712" s="21"/>
       <c r="L712" s="20"/>
     </row>
-    <row r="713" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A713" s="8"/>
       <c r="B713" s="8"/>
       <c r="C713" s="8"/>
       <c r="D713" s="8"/>
-      <c r="E713" s="3"/>
       <c r="K713" s="21"/>
       <c r="L713" s="20"/>
     </row>
-    <row r="714" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A714" s="8"/>
       <c r="B714" s="8"/>
       <c r="C714" s="8"/>
@@ -15845,51 +15820,52 @@
       <c r="K714" s="21"/>
       <c r="L714" s="20"/>
     </row>
-    <row r="715" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A715" s="8"/>
       <c r="B715" s="8"/>
       <c r="C715" s="8"/>
       <c r="D715" s="8"/>
+      <c r="E715" s="3"/>
       <c r="K715" s="21"/>
       <c r="L715" s="20"/>
     </row>
-    <row r="716" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A716" s="8"/>
       <c r="B716" s="8"/>
       <c r="C716" s="8"/>
       <c r="D716" s="8"/>
-      <c r="E716" s="3"/>
+      <c r="H716" s="8"/>
       <c r="K716" s="21"/>
       <c r="L716" s="20"/>
     </row>
-    <row r="717" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A717" s="8"/>
       <c r="B717" s="8"/>
       <c r="C717" s="8"/>
       <c r="D717" s="8"/>
-      <c r="E717" s="3"/>
+      <c r="H717" s="8"/>
       <c r="K717" s="21"/>
       <c r="L717" s="20"/>
     </row>
-    <row r="718" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A718" s="8"/>
       <c r="B718" s="8"/>
       <c r="C718" s="8"/>
       <c r="D718" s="8"/>
-      <c r="H718" s="8"/>
+      <c r="E718" s="3"/>
       <c r="K718" s="21"/>
       <c r="L718" s="20"/>
     </row>
-    <row r="719" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A719" s="8"/>
       <c r="B719" s="8"/>
       <c r="C719" s="8"/>
       <c r="D719" s="8"/>
-      <c r="H719" s="8"/>
       <c r="K719" s="21"/>
       <c r="L719" s="20"/>
-    </row>
-    <row r="720" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M719" s="8"/>
+    </row>
+    <row r="720" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A720" s="8"/>
       <c r="B720" s="8"/>
       <c r="C720" s="8"/>
@@ -15898,41 +15874,41 @@
       <c r="K720" s="21"/>
       <c r="L720" s="20"/>
     </row>
-    <row r="721" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A721" s="8"/>
       <c r="B721" s="8"/>
       <c r="C721" s="8"/>
       <c r="D721" s="8"/>
       <c r="K721" s="21"/>
       <c r="L721" s="20"/>
-      <c r="M721" s="8"/>
-    </row>
-    <row r="722" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="722" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A722" s="8"/>
       <c r="B722" s="8"/>
       <c r="C722" s="8"/>
       <c r="D722" s="8"/>
-      <c r="E722" s="3"/>
       <c r="K722" s="21"/>
       <c r="L722" s="20"/>
     </row>
-    <row r="723" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A723" s="8"/>
       <c r="B723" s="8"/>
       <c r="C723" s="8"/>
       <c r="D723" s="8"/>
+      <c r="E723" s="3"/>
       <c r="K723" s="21"/>
       <c r="L723" s="20"/>
     </row>
-    <row r="724" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A724" s="8"/>
       <c r="B724" s="8"/>
       <c r="C724" s="8"/>
       <c r="D724" s="8"/>
+      <c r="E724" s="3"/>
       <c r="K724" s="21"/>
       <c r="L724" s="20"/>
     </row>
-    <row r="725" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A725" s="8"/>
       <c r="B725" s="8"/>
       <c r="C725" s="8"/>
@@ -15941,7 +15917,7 @@
       <c r="K725" s="21"/>
       <c r="L725" s="20"/>
     </row>
-    <row r="726" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A726" s="8"/>
       <c r="B726" s="8"/>
       <c r="C726" s="8"/>
@@ -15950,25 +15926,23 @@
       <c r="K726" s="21"/>
       <c r="L726" s="20"/>
     </row>
-    <row r="727" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A727" s="8"/>
       <c r="B727" s="8"/>
       <c r="C727" s="8"/>
       <c r="D727" s="8"/>
-      <c r="E727" s="3"/>
       <c r="K727" s="21"/>
       <c r="L727" s="20"/>
     </row>
-    <row r="728" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A728" s="8"/>
       <c r="B728" s="8"/>
       <c r="C728" s="8"/>
       <c r="D728" s="8"/>
-      <c r="E728" s="3"/>
       <c r="K728" s="21"/>
       <c r="L728" s="20"/>
     </row>
-    <row r="729" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A729" s="8"/>
       <c r="B729" s="8"/>
       <c r="C729" s="8"/>
@@ -15976,32 +15950,33 @@
       <c r="K729" s="21"/>
       <c r="L729" s="20"/>
     </row>
-    <row r="730" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A730" s="8"/>
       <c r="B730" s="8"/>
       <c r="C730" s="8"/>
       <c r="D730" s="8"/>
+      <c r="E730" s="3"/>
       <c r="K730" s="21"/>
       <c r="L730" s="20"/>
     </row>
-    <row r="731" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A731" s="8"/>
       <c r="B731" s="8"/>
       <c r="C731" s="8"/>
       <c r="D731" s="8"/>
+      <c r="E731" s="3"/>
       <c r="K731" s="21"/>
       <c r="L731" s="20"/>
     </row>
-    <row r="732" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A732" s="8"/>
       <c r="B732" s="8"/>
       <c r="C732" s="8"/>
       <c r="D732" s="8"/>
-      <c r="E732" s="3"/>
       <c r="K732" s="21"/>
       <c r="L732" s="20"/>
     </row>
-    <row r="733" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A733" s="8"/>
       <c r="B733" s="8"/>
       <c r="C733" s="8"/>
@@ -16010,15 +15985,16 @@
       <c r="K733" s="21"/>
       <c r="L733" s="20"/>
     </row>
-    <row r="734" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A734" s="8"/>
       <c r="B734" s="8"/>
       <c r="C734" s="8"/>
       <c r="D734" s="8"/>
+      <c r="E734" s="3"/>
       <c r="K734" s="21"/>
       <c r="L734" s="20"/>
     </row>
-    <row r="735" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A735" s="8"/>
       <c r="B735" s="8"/>
       <c r="C735" s="8"/>
@@ -16027,7 +16003,7 @@
       <c r="K735" s="21"/>
       <c r="L735" s="20"/>
     </row>
-    <row r="736" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A736" s="8"/>
       <c r="B736" s="8"/>
       <c r="C736" s="8"/>
@@ -16050,7 +16026,7 @@
       <c r="B738" s="8"/>
       <c r="C738" s="8"/>
       <c r="D738" s="8"/>
-      <c r="E738" s="3"/>
+      <c r="H738" s="8"/>
       <c r="K738" s="21"/>
       <c r="L738" s="20"/>
     </row>
@@ -16068,7 +16044,6 @@
       <c r="B740" s="8"/>
       <c r="C740" s="8"/>
       <c r="D740" s="8"/>
-      <c r="H740" s="8"/>
       <c r="K740" s="21"/>
       <c r="L740" s="20"/>
     </row>
@@ -16086,6 +16061,7 @@
       <c r="B742" s="8"/>
       <c r="C742" s="8"/>
       <c r="D742" s="8"/>
+      <c r="E742" s="3"/>
       <c r="K742" s="21"/>
       <c r="L742" s="20"/>
     </row>
@@ -16130,7 +16106,6 @@
       <c r="B747" s="8"/>
       <c r="C747" s="8"/>
       <c r="D747" s="8"/>
-      <c r="E747" s="3"/>
       <c r="K747" s="21"/>
       <c r="L747" s="20"/>
     </row>
@@ -16148,6 +16123,7 @@
       <c r="B749" s="8"/>
       <c r="C749" s="8"/>
       <c r="D749" s="8"/>
+      <c r="E749" s="3"/>
       <c r="K749" s="21"/>
       <c r="L749" s="20"/>
     </row>
@@ -16165,7 +16141,7 @@
       <c r="B751" s="8"/>
       <c r="C751" s="8"/>
       <c r="D751" s="8"/>
-      <c r="E751" s="3"/>
+      <c r="H751" s="8"/>
       <c r="K751" s="21"/>
       <c r="L751" s="20"/>
     </row>
@@ -16174,7 +16150,7 @@
       <c r="B752" s="8"/>
       <c r="C752" s="8"/>
       <c r="D752" s="8"/>
-      <c r="E752" s="3"/>
+      <c r="H752" s="8"/>
       <c r="K752" s="21"/>
       <c r="L752" s="20"/>
     </row>
@@ -16201,7 +16177,7 @@
       <c r="B755" s="8"/>
       <c r="C755" s="8"/>
       <c r="D755" s="8"/>
-      <c r="H755" s="8"/>
+      <c r="E755" s="3"/>
       <c r="K755" s="21"/>
       <c r="L755" s="20"/>
     </row>
@@ -16210,7 +16186,8 @@
       <c r="B756" s="8"/>
       <c r="C756" s="8"/>
       <c r="D756" s="8"/>
-      <c r="H756" s="8"/>
+      <c r="E756" s="3"/>
+      <c r="G756" s="8"/>
       <c r="K756" s="21"/>
       <c r="L756" s="20"/>
     </row>
@@ -16229,7 +16206,6 @@
       <c r="C758" s="8"/>
       <c r="D758" s="8"/>
       <c r="E758" s="3"/>
-      <c r="G758" s="8"/>
       <c r="K758" s="21"/>
       <c r="L758" s="20"/>
     </row>
@@ -16238,7 +16214,6 @@
       <c r="B759" s="8"/>
       <c r="C759" s="8"/>
       <c r="D759" s="8"/>
-      <c r="E759" s="3"/>
       <c r="K759" s="21"/>
       <c r="L759" s="20"/>
     </row>
@@ -16256,6 +16231,7 @@
       <c r="B761" s="8"/>
       <c r="C761" s="8"/>
       <c r="D761" s="8"/>
+      <c r="E761" s="3"/>
       <c r="K761" s="21"/>
       <c r="L761" s="20"/>
     </row>
@@ -16265,6 +16241,7 @@
       <c r="C762" s="8"/>
       <c r="D762" s="8"/>
       <c r="E762" s="3"/>
+      <c r="G762" s="8"/>
       <c r="K762" s="21"/>
       <c r="L762" s="20"/>
     </row>
@@ -16273,44 +16250,43 @@
       <c r="B763" s="8"/>
       <c r="C763" s="8"/>
       <c r="D763" s="8"/>
-      <c r="E763" s="3"/>
       <c r="K763" s="21"/>
       <c r="L763" s="20"/>
+      <c r="M763" s="8"/>
     </row>
     <row r="764" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A764" s="8"/>
       <c r="B764" s="8"/>
       <c r="C764" s="8"/>
       <c r="D764" s="8"/>
-      <c r="E764" s="3"/>
-      <c r="G764" s="8"/>
       <c r="K764" s="21"/>
       <c r="L764" s="20"/>
+      <c r="M764" s="8"/>
     </row>
     <row r="765" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A765" s="8"/>
       <c r="B765" s="8"/>
       <c r="C765" s="8"/>
       <c r="D765" s="8"/>
+      <c r="E765" s="3"/>
       <c r="K765" s="21"/>
       <c r="L765" s="20"/>
-      <c r="M765" s="8"/>
     </row>
     <row r="766" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A766" s="8"/>
       <c r="B766" s="8"/>
       <c r="C766" s="8"/>
       <c r="D766" s="8"/>
+      <c r="E766" s="3"/>
       <c r="K766" s="21"/>
       <c r="L766" s="20"/>
-      <c r="M766" s="8"/>
     </row>
     <row r="767" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A767" s="8"/>
       <c r="B767" s="8"/>
       <c r="C767" s="8"/>
       <c r="D767" s="8"/>
-      <c r="E767" s="3"/>
+      <c r="E767" s="16"/>
       <c r="K767" s="21"/>
       <c r="L767" s="20"/>
     </row>
@@ -16328,7 +16304,7 @@
       <c r="B769" s="8"/>
       <c r="C769" s="8"/>
       <c r="D769" s="8"/>
-      <c r="E769" s="16"/>
+      <c r="E769" s="3"/>
       <c r="K769" s="21"/>
       <c r="L769" s="20"/>
     </row>
@@ -16338,6 +16314,7 @@
       <c r="C770" s="8"/>
       <c r="D770" s="8"/>
       <c r="E770" s="3"/>
+      <c r="G770" s="8"/>
       <c r="K770" s="21"/>
       <c r="L770" s="20"/>
     </row>
@@ -16355,8 +16332,6 @@
       <c r="B772" s="8"/>
       <c r="C772" s="8"/>
       <c r="D772" s="8"/>
-      <c r="E772" s="3"/>
-      <c r="G772" s="8"/>
       <c r="K772" s="21"/>
       <c r="L772" s="20"/>
     </row>
@@ -16365,7 +16340,6 @@
       <c r="B773" s="8"/>
       <c r="C773" s="8"/>
       <c r="D773" s="8"/>
-      <c r="E773" s="3"/>
       <c r="K773" s="21"/>
       <c r="L773" s="20"/>
     </row>
@@ -16374,6 +16348,7 @@
       <c r="B774" s="8"/>
       <c r="C774" s="8"/>
       <c r="D774" s="8"/>
+      <c r="E774" s="3"/>
       <c r="K774" s="21"/>
       <c r="L774" s="20"/>
     </row>
@@ -16384,6 +16359,7 @@
       <c r="D775" s="8"/>
       <c r="K775" s="21"/>
       <c r="L775" s="20"/>
+      <c r="M775" s="8"/>
     </row>
     <row r="776" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A776" s="8"/>
@@ -16399,16 +16375,15 @@
       <c r="B777" s="8"/>
       <c r="C777" s="8"/>
       <c r="D777" s="8"/>
+      <c r="E777" s="3"/>
       <c r="K777" s="21"/>
       <c r="L777" s="20"/>
-      <c r="M777" s="8"/>
     </row>
     <row r="778" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A778" s="8"/>
       <c r="B778" s="8"/>
       <c r="C778" s="8"/>
       <c r="D778" s="8"/>
-      <c r="E778" s="3"/>
       <c r="K778" s="21"/>
       <c r="L778" s="20"/>
     </row>
@@ -16416,34 +16391,34 @@
       <c r="A779" s="8"/>
       <c r="B779" s="8"/>
       <c r="C779" s="8"/>
-      <c r="D779" s="8"/>
       <c r="E779" s="3"/>
       <c r="K779" s="21"/>
       <c r="L779" s="20"/>
     </row>
     <row r="780" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A780" s="8"/>
       <c r="B780" s="8"/>
-      <c r="C780" s="8"/>
-      <c r="D780" s="8"/>
-      <c r="K780" s="21"/>
-      <c r="L780" s="20"/>
+      <c r="M780" s="8"/>
     </row>
     <row r="781" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A781" s="8"/>
       <c r="B781" s="8"/>
-      <c r="C781" s="8"/>
-      <c r="E781" s="3"/>
-      <c r="K781" s="21"/>
-      <c r="L781" s="20"/>
+      <c r="M781" s="8"/>
     </row>
     <row r="782" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A782" s="8"/>
       <c r="B782" s="8"/>
-      <c r="M782" s="8"/>
+      <c r="C782" s="8"/>
+      <c r="D782" s="8"/>
+      <c r="K782" s="21"/>
+      <c r="L782" s="20"/>
     </row>
     <row r="783" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A783" s="8"/>
       <c r="B783" s="8"/>
-      <c r="M783" s="8"/>
+      <c r="C783" s="8"/>
+      <c r="D783" s="8"/>
+      <c r="E783" s="3"/>
+      <c r="K783" s="21"/>
+      <c r="L783" s="20"/>
     </row>
     <row r="784" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A784" s="8"/>
@@ -16467,6 +16442,7 @@
       <c r="B786" s="8"/>
       <c r="C786" s="8"/>
       <c r="D786" s="8"/>
+      <c r="E786" s="16"/>
       <c r="K786" s="21"/>
       <c r="L786" s="20"/>
     </row>
@@ -16484,7 +16460,7 @@
       <c r="B788" s="8"/>
       <c r="C788" s="8"/>
       <c r="D788" s="8"/>
-      <c r="E788" s="16"/>
+      <c r="E788" s="3"/>
       <c r="K788" s="21"/>
       <c r="L788" s="20"/>
     </row>
@@ -16500,9 +16476,8 @@
     <row r="790" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A790" s="8"/>
       <c r="B790" s="8"/>
-      <c r="C790" s="8"/>
+      <c r="C790" s="26"/>
       <c r="D790" s="8"/>
-      <c r="E790" s="3"/>
       <c r="K790" s="21"/>
       <c r="L790" s="20"/>
     </row>
@@ -16518,8 +16493,9 @@
     <row r="792" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A792" s="8"/>
       <c r="B792" s="8"/>
-      <c r="C792" s="26"/>
+      <c r="C792" s="8"/>
       <c r="D792" s="8"/>
+      <c r="E792" s="3"/>
       <c r="K792" s="21"/>
       <c r="L792" s="20"/>
     </row>
@@ -16527,42 +16503,43 @@
       <c r="A793" s="8"/>
       <c r="B793" s="8"/>
       <c r="C793" s="8"/>
-      <c r="D793" s="8"/>
       <c r="E793" s="3"/>
       <c r="K793" s="21"/>
       <c r="L793" s="20"/>
     </row>
     <row r="794" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A794" s="8"/>
-      <c r="B794" s="8"/>
-      <c r="C794" s="8"/>
-      <c r="D794" s="8"/>
-      <c r="E794" s="3"/>
-      <c r="K794" s="21"/>
-      <c r="L794" s="20"/>
+      <c r="B794" s="40"/>
+      <c r="C794" s="40"/>
+      <c r="D794" s="42"/>
+      <c r="E794" s="11"/>
+      <c r="F794" s="42"/>
+      <c r="G794" s="42"/>
+      <c r="H794" s="42"/>
+      <c r="I794" s="42"/>
+      <c r="J794" s="42"/>
+      <c r="K794" s="23"/>
+      <c r="L794" s="24"/>
+      <c r="M794" s="42"/>
     </row>
     <row r="795" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A795" s="8"/>
       <c r="B795" s="8"/>
       <c r="C795" s="8"/>
+      <c r="D795" s="8"/>
       <c r="E795" s="3"/>
+      <c r="H795" s="8"/>
       <c r="K795" s="21"/>
       <c r="L795" s="20"/>
     </row>
     <row r="796" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A796" s="8"/>
-      <c r="B796" s="40"/>
-      <c r="C796" s="40"/>
-      <c r="D796" s="42"/>
-      <c r="E796" s="11"/>
-      <c r="F796" s="42"/>
-      <c r="G796" s="42"/>
-      <c r="H796" s="42"/>
-      <c r="I796" s="42"/>
-      <c r="J796" s="42"/>
-      <c r="K796" s="23"/>
-      <c r="L796" s="24"/>
-      <c r="M796" s="42"/>
+      <c r="B796" s="8"/>
+      <c r="C796" s="8"/>
+      <c r="D796" s="8"/>
+      <c r="E796" s="3"/>
+      <c r="K796" s="21"/>
+      <c r="L796" s="20"/>
     </row>
     <row r="797" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A797" s="8"/>
@@ -16570,7 +16547,6 @@
       <c r="C797" s="8"/>
       <c r="D797" s="8"/>
       <c r="E797" s="3"/>
-      <c r="H797" s="8"/>
       <c r="K797" s="21"/>
       <c r="L797" s="20"/>
     </row>
@@ -16606,7 +16582,6 @@
       <c r="B801" s="8"/>
       <c r="C801" s="8"/>
       <c r="D801" s="8"/>
-      <c r="E801" s="3"/>
       <c r="K801" s="21"/>
       <c r="L801" s="20"/>
     </row>
@@ -16624,6 +16599,7 @@
       <c r="B803" s="8"/>
       <c r="C803" s="8"/>
       <c r="D803" s="8"/>
+      <c r="E803" s="3"/>
       <c r="K803" s="21"/>
       <c r="L803" s="20"/>
     </row>
@@ -16641,7 +16617,6 @@
       <c r="B805" s="8"/>
       <c r="C805" s="8"/>
       <c r="D805" s="8"/>
-      <c r="E805" s="3"/>
       <c r="K805" s="21"/>
       <c r="L805" s="20"/>
     </row>
@@ -16659,6 +16634,7 @@
       <c r="B807" s="8"/>
       <c r="C807" s="8"/>
       <c r="D807" s="8"/>
+      <c r="E807" s="3"/>
       <c r="K807" s="21"/>
       <c r="L807" s="20"/>
     </row>
@@ -16703,7 +16679,6 @@
       <c r="B812" s="8"/>
       <c r="C812" s="8"/>
       <c r="D812" s="8"/>
-      <c r="E812" s="3"/>
       <c r="K812" s="21"/>
       <c r="L812" s="20"/>
     </row>
@@ -16721,6 +16696,7 @@
       <c r="B814" s="8"/>
       <c r="C814" s="8"/>
       <c r="D814" s="8"/>
+      <c r="E814" s="3"/>
       <c r="K814" s="21"/>
       <c r="L814" s="20"/>
     </row>
@@ -16729,7 +16705,6 @@
       <c r="B815" s="8"/>
       <c r="C815" s="8"/>
       <c r="D815" s="8"/>
-      <c r="E815" s="3"/>
       <c r="K815" s="21"/>
       <c r="L815" s="20"/>
     </row>
@@ -16747,6 +16722,7 @@
       <c r="B817" s="8"/>
       <c r="C817" s="8"/>
       <c r="D817" s="8"/>
+      <c r="E817" s="3"/>
       <c r="K817" s="21"/>
       <c r="L817" s="20"/>
     </row>
@@ -16755,7 +16731,6 @@
       <c r="B818" s="8"/>
       <c r="C818" s="8"/>
       <c r="D818" s="8"/>
-      <c r="E818" s="3"/>
       <c r="K818" s="21"/>
       <c r="L818" s="20"/>
     </row>
@@ -16763,7 +16738,6 @@
       <c r="A819" s="8"/>
       <c r="B819" s="8"/>
       <c r="C819" s="8"/>
-      <c r="D819" s="8"/>
       <c r="E819" s="3"/>
       <c r="K819" s="21"/>
       <c r="L819" s="20"/>
@@ -16772,7 +16746,7 @@
       <c r="A820" s="8"/>
       <c r="B820" s="8"/>
       <c r="C820" s="8"/>
-      <c r="D820" s="8"/>
+      <c r="E820" s="3"/>
       <c r="K820" s="21"/>
       <c r="L820" s="20"/>
     </row>
@@ -16780,6 +16754,7 @@
       <c r="A821" s="8"/>
       <c r="B821" s="8"/>
       <c r="C821" s="8"/>
+      <c r="D821" s="8"/>
       <c r="E821" s="3"/>
       <c r="K821" s="21"/>
       <c r="L821" s="20"/>
@@ -16788,6 +16763,7 @@
       <c r="A822" s="8"/>
       <c r="B822" s="8"/>
       <c r="C822" s="8"/>
+      <c r="D822" s="8"/>
       <c r="E822" s="3"/>
       <c r="K822" s="21"/>
       <c r="L822" s="20"/>
@@ -16815,7 +16791,6 @@
       <c r="B825" s="8"/>
       <c r="C825" s="8"/>
       <c r="D825" s="8"/>
-      <c r="E825" s="3"/>
       <c r="K825" s="21"/>
       <c r="L825" s="20"/>
     </row>
@@ -16832,23 +16807,19 @@
       <c r="A827" s="8"/>
       <c r="B827" s="8"/>
       <c r="C827" s="8"/>
-      <c r="D827" s="8"/>
       <c r="K827" s="21"/>
       <c r="L827" s="20"/>
     </row>
     <row r="828" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A828" s="8"/>
       <c r="B828" s="8"/>
-      <c r="C828" s="8"/>
-      <c r="D828" s="8"/>
-      <c r="E828" s="3"/>
-      <c r="K828" s="21"/>
-      <c r="L828" s="20"/>
+      <c r="M828" s="8"/>
     </row>
     <row r="829" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A829" s="8"/>
       <c r="B829" s="8"/>
       <c r="C829" s="8"/>
+      <c r="D829" s="8"/>
+      <c r="E829" s="3"/>
       <c r="K829" s="21"/>
       <c r="L829" s="20"/>
     </row>
@@ -16857,24 +16828,27 @@
       <c r="M830" s="8"/>
     </row>
     <row r="831" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A831" s="8"/>
       <c r="B831" s="8"/>
-      <c r="C831" s="8"/>
-      <c r="D831" s="8"/>
-      <c r="E831" s="3"/>
-      <c r="K831" s="21"/>
-      <c r="L831" s="20"/>
+      <c r="M831" s="8"/>
     </row>
     <row r="832" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B832" s="8"/>
       <c r="M832" s="8"/>
     </row>
     <row r="833" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A833" s="8"/>
       <c r="B833" s="8"/>
-      <c r="M833" s="8"/>
+      <c r="C833" s="8"/>
+      <c r="D833" s="8"/>
+      <c r="E833" s="3"/>
+      <c r="K833" s="21"/>
+      <c r="L833" s="20"/>
     </row>
     <row r="834" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A834" s="8"/>
       <c r="B834" s="8"/>
+      <c r="C834" s="8"/>
+      <c r="D834" s="8"/>
       <c r="M834" s="8"/>
     </row>
     <row r="835" spans="1:13" x14ac:dyDescent="0.2">
@@ -16882,7 +16856,6 @@
       <c r="B835" s="8"/>
       <c r="C835" s="8"/>
       <c r="D835" s="8"/>
-      <c r="E835" s="3"/>
       <c r="K835" s="21"/>
       <c r="L835" s="20"/>
     </row>
@@ -16891,13 +16864,16 @@
       <c r="B836" s="8"/>
       <c r="C836" s="8"/>
       <c r="D836" s="8"/>
-      <c r="M836" s="8"/>
+      <c r="E836" s="3"/>
+      <c r="K836" s="21"/>
+      <c r="L836" s="20"/>
     </row>
     <row r="837" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A837" s="8"/>
       <c r="B837" s="8"/>
       <c r="C837" s="8"/>
       <c r="D837" s="8"/>
+      <c r="E837" s="3"/>
       <c r="K837" s="21"/>
       <c r="L837" s="20"/>
     </row>
@@ -16916,6 +16892,7 @@
       <c r="C839" s="8"/>
       <c r="D839" s="8"/>
       <c r="E839" s="3"/>
+      <c r="G839" s="8"/>
       <c r="K839" s="21"/>
       <c r="L839" s="20"/>
     </row>
@@ -16925,6 +16902,7 @@
       <c r="C840" s="8"/>
       <c r="D840" s="8"/>
       <c r="E840" s="3"/>
+      <c r="G840" s="8"/>
       <c r="K840" s="21"/>
       <c r="L840" s="20"/>
     </row>
@@ -16933,18 +16911,15 @@
       <c r="B841" s="8"/>
       <c r="C841" s="8"/>
       <c r="D841" s="8"/>
-      <c r="E841" s="3"/>
-      <c r="G841" s="8"/>
       <c r="K841" s="21"/>
       <c r="L841" s="20"/>
+      <c r="M841" s="8"/>
     </row>
     <row r="842" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A842" s="8"/>
       <c r="B842" s="8"/>
       <c r="C842" s="8"/>
       <c r="D842" s="8"/>
-      <c r="E842" s="3"/>
-      <c r="G842" s="8"/>
       <c r="K842" s="21"/>
       <c r="L842" s="20"/>
     </row>
@@ -16955,7 +16930,6 @@
       <c r="D843" s="8"/>
       <c r="K843" s="21"/>
       <c r="L843" s="20"/>
-      <c r="M843" s="8"/>
     </row>
     <row r="844" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A844" s="8"/>
@@ -16969,7 +16943,8 @@
       <c r="A845" s="8"/>
       <c r="B845" s="8"/>
       <c r="C845" s="8"/>
-      <c r="D845" s="8"/>
+      <c r="E845" s="3"/>
+      <c r="I845" s="8"/>
       <c r="K845" s="21"/>
       <c r="L845" s="20"/>
     </row>
@@ -16980,13 +16955,14 @@
       <c r="D846" s="8"/>
       <c r="K846" s="21"/>
       <c r="L846" s="20"/>
+      <c r="M846" s="8"/>
     </row>
     <row r="847" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A847" s="8"/>
       <c r="B847" s="8"/>
       <c r="C847" s="8"/>
+      <c r="D847" s="8"/>
       <c r="E847" s="3"/>
-      <c r="I847" s="8"/>
       <c r="K847" s="21"/>
       <c r="L847" s="20"/>
     </row>
@@ -16995,16 +16971,15 @@
       <c r="B848" s="8"/>
       <c r="C848" s="8"/>
       <c r="D848" s="8"/>
+      <c r="E848" s="3"/>
       <c r="K848" s="21"/>
       <c r="L848" s="20"/>
-      <c r="M848" s="8"/>
     </row>
     <row r="849" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A849" s="8"/>
       <c r="B849" s="8"/>
       <c r="C849" s="8"/>
       <c r="D849" s="8"/>
-      <c r="E849" s="3"/>
       <c r="K849" s="21"/>
       <c r="L849" s="20"/>
     </row>
@@ -17013,7 +16988,6 @@
       <c r="B850" s="8"/>
       <c r="C850" s="8"/>
       <c r="D850" s="8"/>
-      <c r="E850" s="3"/>
       <c r="K850" s="21"/>
       <c r="L850" s="20"/>
     </row>
@@ -17022,6 +16996,7 @@
       <c r="B851" s="8"/>
       <c r="C851" s="8"/>
       <c r="D851" s="8"/>
+      <c r="E851" s="3"/>
       <c r="K851" s="21"/>
       <c r="L851" s="20"/>
     </row>
@@ -17030,6 +17005,7 @@
       <c r="B852" s="8"/>
       <c r="C852" s="8"/>
       <c r="D852" s="8"/>
+      <c r="E852" s="3"/>
       <c r="K852" s="21"/>
       <c r="L852" s="20"/>
     </row>
@@ -17092,35 +17068,30 @@
       <c r="B859" s="8"/>
       <c r="C859" s="8"/>
       <c r="D859" s="8"/>
-      <c r="E859" s="3"/>
       <c r="K859" s="21"/>
       <c r="L859" s="20"/>
+      <c r="M859" s="8"/>
     </row>
     <row r="860" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A860" s="8"/>
       <c r="B860" s="8"/>
       <c r="C860" s="8"/>
       <c r="D860" s="8"/>
-      <c r="E860" s="3"/>
       <c r="K860" s="21"/>
       <c r="L860" s="20"/>
+      <c r="M860" s="8"/>
     </row>
     <row r="861" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A861" s="8"/>
       <c r="B861" s="8"/>
       <c r="C861" s="8"/>
       <c r="D861" s="8"/>
+      <c r="E861" s="3"/>
       <c r="K861" s="21"/>
       <c r="L861" s="20"/>
-      <c r="M861" s="8"/>
     </row>
     <row r="862" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A862" s="8"/>
       <c r="B862" s="8"/>
-      <c r="C862" s="8"/>
-      <c r="D862" s="8"/>
-      <c r="K862" s="21"/>
-      <c r="L862" s="20"/>
       <c r="M862" s="8"/>
     </row>
     <row r="863" spans="1:13" x14ac:dyDescent="0.2">
@@ -17133,8 +17104,13 @@
       <c r="L863" s="20"/>
     </row>
     <row r="864" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A864" s="8"/>
       <c r="B864" s="8"/>
-      <c r="M864" s="8"/>
+      <c r="C864" s="8"/>
+      <c r="D864" s="8"/>
+      <c r="E864" s="3"/>
+      <c r="K864" s="21"/>
+      <c r="L864" s="20"/>
     </row>
     <row r="865" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A865" s="8"/>
@@ -17159,7 +17135,6 @@
       <c r="B867" s="8"/>
       <c r="C867" s="8"/>
       <c r="D867" s="8"/>
-      <c r="E867" s="3"/>
       <c r="K867" s="21"/>
       <c r="L867" s="20"/>
     </row>
@@ -17185,7 +17160,6 @@
       <c r="B870" s="8"/>
       <c r="C870" s="8"/>
       <c r="D870" s="8"/>
-      <c r="E870" s="3"/>
       <c r="K870" s="21"/>
       <c r="L870" s="20"/>
     </row>
@@ -17194,6 +17168,7 @@
       <c r="B871" s="8"/>
       <c r="C871" s="8"/>
       <c r="D871" s="8"/>
+      <c r="E871" s="3"/>
       <c r="K871" s="21"/>
       <c r="L871" s="20"/>
     </row>
@@ -17202,6 +17177,7 @@
       <c r="B872" s="8"/>
       <c r="C872" s="8"/>
       <c r="D872" s="8"/>
+      <c r="E872" s="3"/>
       <c r="K872" s="21"/>
       <c r="L872" s="20"/>
     </row>
@@ -17237,7 +17213,6 @@
       <c r="B876" s="8"/>
       <c r="C876" s="8"/>
       <c r="D876" s="8"/>
-      <c r="E876" s="3"/>
       <c r="K876" s="21"/>
       <c r="L876" s="20"/>
     </row>
@@ -17263,7 +17238,7 @@
       <c r="B879" s="8"/>
       <c r="C879" s="8"/>
       <c r="D879" s="8"/>
-      <c r="E879" s="3"/>
+      <c r="E879" s="16"/>
       <c r="K879" s="21"/>
       <c r="L879" s="20"/>
     </row>
@@ -17272,6 +17247,7 @@
       <c r="B880" s="8"/>
       <c r="C880" s="8"/>
       <c r="D880" s="8"/>
+      <c r="E880" s="3"/>
       <c r="K880" s="21"/>
       <c r="L880" s="20"/>
     </row>
@@ -17280,7 +17256,7 @@
       <c r="B881" s="8"/>
       <c r="C881" s="8"/>
       <c r="D881" s="8"/>
-      <c r="E881" s="16"/>
+      <c r="E881" s="3"/>
       <c r="K881" s="21"/>
       <c r="L881" s="20"/>
     </row>
@@ -17370,7 +17346,6 @@
       <c r="B891" s="8"/>
       <c r="C891" s="8"/>
       <c r="D891" s="8"/>
-      <c r="E891" s="3"/>
       <c r="K891" s="21"/>
       <c r="L891" s="20"/>
     </row>
@@ -17388,6 +17363,7 @@
       <c r="B893" s="8"/>
       <c r="C893" s="8"/>
       <c r="D893" s="8"/>
+      <c r="E893" s="3"/>
       <c r="K893" s="21"/>
       <c r="L893" s="20"/>
     </row>
@@ -17405,7 +17381,6 @@
       <c r="B895" s="8"/>
       <c r="C895" s="8"/>
       <c r="D895" s="8"/>
-      <c r="E895" s="3"/>
       <c r="K895" s="21"/>
       <c r="L895" s="20"/>
     </row>
@@ -17423,6 +17398,7 @@
       <c r="B897" s="8"/>
       <c r="C897" s="8"/>
       <c r="D897" s="8"/>
+      <c r="E897" s="3"/>
       <c r="K897" s="21"/>
       <c r="L897" s="20"/>
     </row>
@@ -17475,7 +17451,6 @@
       <c r="A903" s="8"/>
       <c r="B903" s="8"/>
       <c r="C903" s="8"/>
-      <c r="D903" s="8"/>
       <c r="E903" s="3"/>
       <c r="K903" s="21"/>
       <c r="L903" s="20"/>
@@ -17484,7 +17459,6 @@
       <c r="A904" s="8"/>
       <c r="B904" s="8"/>
       <c r="C904" s="8"/>
-      <c r="D904" s="8"/>
       <c r="E904" s="3"/>
       <c r="K904" s="21"/>
       <c r="L904" s="20"/>
@@ -17506,41 +17480,43 @@
       <c r="L906" s="20"/>
     </row>
     <row r="907" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A907" s="8"/>
-      <c r="B907" s="8"/>
-      <c r="C907" s="8"/>
-      <c r="E907" s="3"/>
-      <c r="K907" s="21"/>
-      <c r="L907" s="20"/>
+      <c r="A907" s="42"/>
+      <c r="B907" s="40"/>
+      <c r="C907" s="42"/>
+      <c r="D907" s="42"/>
+      <c r="E907" s="42"/>
+      <c r="F907" s="42"/>
+      <c r="G907" s="42"/>
+      <c r="H907" s="42"/>
+      <c r="I907" s="42"/>
+      <c r="J907" s="42"/>
+      <c r="K907" s="42"/>
+      <c r="L907" s="42"/>
+      <c r="M907" s="40"/>
     </row>
     <row r="908" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A908" s="8"/>
       <c r="B908" s="8"/>
       <c r="C908" s="8"/>
-      <c r="E908" s="3"/>
+      <c r="D908" s="8"/>
       <c r="K908" s="21"/>
       <c r="L908" s="20"/>
     </row>
     <row r="909" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A909" s="42"/>
-      <c r="B909" s="40"/>
-      <c r="C909" s="42"/>
-      <c r="D909" s="42"/>
-      <c r="E909" s="42"/>
-      <c r="F909" s="42"/>
-      <c r="G909" s="42"/>
-      <c r="H909" s="42"/>
-      <c r="I909" s="42"/>
-      <c r="J909" s="42"/>
-      <c r="K909" s="42"/>
-      <c r="L909" s="42"/>
-      <c r="M909" s="40"/>
+      <c r="A909" s="8"/>
+      <c r="B909" s="8"/>
+      <c r="C909" s="8"/>
+      <c r="D909" s="8"/>
+      <c r="E909" s="3"/>
+      <c r="K909" s="21"/>
+      <c r="L909" s="20"/>
     </row>
     <row r="910" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A910" s="8"/>
       <c r="B910" s="8"/>
       <c r="C910" s="8"/>
       <c r="D910" s="8"/>
+      <c r="E910" s="3"/>
       <c r="K910" s="21"/>
       <c r="L910" s="20"/>
     </row>
@@ -17549,34 +17525,34 @@
       <c r="B911" s="8"/>
       <c r="C911" s="8"/>
       <c r="D911" s="8"/>
-      <c r="E911" s="3"/>
       <c r="K911" s="21"/>
       <c r="L911" s="20"/>
     </row>
     <row r="912" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A912" s="8"/>
       <c r="B912" s="8"/>
       <c r="C912" s="8"/>
       <c r="D912" s="8"/>
-      <c r="E912" s="3"/>
       <c r="K912" s="21"/>
       <c r="L912" s="20"/>
+      <c r="M912" s="8"/>
     </row>
     <row r="913" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A913" s="8"/>
       <c r="B913" s="8"/>
       <c r="C913" s="8"/>
       <c r="D913" s="8"/>
+      <c r="E913" s="3"/>
       <c r="K913" s="21"/>
       <c r="L913" s="20"/>
     </row>
     <row r="914" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A914" s="8"/>
       <c r="B914" s="8"/>
       <c r="C914" s="8"/>
       <c r="D914" s="8"/>
+      <c r="E914" s="3"/>
       <c r="K914" s="21"/>
       <c r="L914" s="20"/>
-      <c r="M914" s="8"/>
     </row>
     <row r="915" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A915" s="8"/>
@@ -17588,13 +17564,12 @@
       <c r="L915" s="20"/>
     </row>
     <row r="916" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A916" s="8"/>
       <c r="B916" s="8"/>
       <c r="C916" s="8"/>
       <c r="D916" s="8"/>
-      <c r="E916" s="3"/>
       <c r="K916" s="21"/>
       <c r="L916" s="20"/>
+      <c r="M916" s="8"/>
     </row>
     <row r="917" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A917" s="8"/>
@@ -17606,19 +17581,18 @@
       <c r="L917" s="20"/>
     </row>
     <row r="918" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A918" s="8"/>
       <c r="B918" s="8"/>
       <c r="C918" s="8"/>
       <c r="D918" s="8"/>
       <c r="K918" s="21"/>
       <c r="L918" s="20"/>
-      <c r="M918" s="8"/>
     </row>
     <row r="919" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A919" s="8"/>
       <c r="B919" s="8"/>
       <c r="C919" s="8"/>
       <c r="D919" s="8"/>
-      <c r="E919" s="3"/>
       <c r="K919" s="21"/>
       <c r="L919" s="20"/>
     </row>
@@ -17627,6 +17601,7 @@
       <c r="B920" s="8"/>
       <c r="C920" s="8"/>
       <c r="D920" s="8"/>
+      <c r="E920" s="3"/>
       <c r="K920" s="21"/>
       <c r="L920" s="20"/>
     </row>
@@ -17635,6 +17610,7 @@
       <c r="B921" s="8"/>
       <c r="C921" s="8"/>
       <c r="D921" s="8"/>
+      <c r="E921" s="3"/>
       <c r="K921" s="21"/>
       <c r="L921" s="20"/>
     </row>
@@ -17670,7 +17646,6 @@
       <c r="B925" s="8"/>
       <c r="C925" s="8"/>
       <c r="D925" s="8"/>
-      <c r="E925" s="3"/>
       <c r="K925" s="21"/>
       <c r="L925" s="20"/>
     </row>
@@ -17679,17 +17654,16 @@
       <c r="B926" s="8"/>
       <c r="C926" s="8"/>
       <c r="D926" s="8"/>
-      <c r="E926" s="3"/>
       <c r="K926" s="21"/>
       <c r="L926" s="20"/>
     </row>
     <row r="927" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A927" s="8"/>
       <c r="B927" s="8"/>
       <c r="C927" s="8"/>
       <c r="D927" s="8"/>
       <c r="K927" s="21"/>
       <c r="L927" s="20"/>
+      <c r="M927" s="8"/>
     </row>
     <row r="928" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A928" s="8"/>
@@ -17699,31 +17673,33 @@
       <c r="K928" s="21"/>
       <c r="L928" s="20"/>
     </row>
-    <row r="929" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A929" s="8"/>
       <c r="B929" s="8"/>
       <c r="C929" s="8"/>
       <c r="D929" s="8"/>
       <c r="K929" s="21"/>
       <c r="L929" s="20"/>
-      <c r="M929" s="8"/>
-    </row>
-    <row r="930" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="930" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A930" s="8"/>
       <c r="B930" s="8"/>
       <c r="C930" s="8"/>
       <c r="D930" s="8"/>
+      <c r="E930" s="3"/>
       <c r="K930" s="21"/>
       <c r="L930" s="20"/>
     </row>
-    <row r="931" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A931" s="8"/>
       <c r="B931" s="8"/>
       <c r="C931" s="8"/>
       <c r="D931" s="8"/>
+      <c r="E931" s="3"/>
       <c r="K931" s="21"/>
       <c r="L931" s="20"/>
     </row>
-    <row r="932" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A932" s="8"/>
       <c r="B932" s="8"/>
       <c r="C932" s="8"/>
@@ -17732,7 +17708,7 @@
       <c r="K932" s="21"/>
       <c r="L932" s="20"/>
     </row>
-    <row r="933" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A933" s="8"/>
       <c r="B933" s="8"/>
       <c r="C933" s="8"/>
@@ -17741,7 +17717,7 @@
       <c r="K933" s="21"/>
       <c r="L933" s="20"/>
     </row>
-    <row r="934" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A934" s="8"/>
       <c r="B934" s="8"/>
       <c r="C934" s="8"/>
@@ -17750,7 +17726,7 @@
       <c r="K934" s="21"/>
       <c r="L934" s="20"/>
     </row>
-    <row r="935" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A935" s="8"/>
       <c r="B935" s="8"/>
       <c r="C935" s="8"/>
@@ -17759,49 +17735,49 @@
       <c r="K935" s="21"/>
       <c r="L935" s="20"/>
     </row>
-    <row r="936" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A936" s="8"/>
       <c r="B936" s="8"/>
       <c r="C936" s="8"/>
-      <c r="D936" s="8"/>
       <c r="E936" s="3"/>
       <c r="K936" s="21"/>
       <c r="L936" s="20"/>
     </row>
-    <row r="937" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A937" s="8"/>
       <c r="B937" s="8"/>
       <c r="C937" s="8"/>
-      <c r="D937" s="8"/>
-      <c r="E937" s="3"/>
+      <c r="E937" s="16"/>
       <c r="K937" s="21"/>
       <c r="L937" s="20"/>
     </row>
-    <row r="938" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A938" s="8"/>
       <c r="B938" s="8"/>
       <c r="C938" s="8"/>
       <c r="E938" s="3"/>
-      <c r="K938" s="21"/>
+      <c r="K938" s="7"/>
       <c r="L938" s="20"/>
     </row>
-    <row r="939" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A939" s="8"/>
       <c r="B939" s="8"/>
       <c r="C939" s="8"/>
-      <c r="E939" s="16"/>
-      <c r="K939" s="21"/>
+      <c r="D939" s="8"/>
+      <c r="E939" s="3"/>
+      <c r="K939" s="7"/>
       <c r="L939" s="20"/>
     </row>
-    <row r="940" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A940" s="8"/>
       <c r="B940" s="8"/>
       <c r="C940" s="8"/>
+      <c r="D940" s="8"/>
       <c r="E940" s="3"/>
       <c r="K940" s="7"/>
       <c r="L940" s="20"/>
     </row>
-    <row r="941" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A941" s="8"/>
       <c r="B941" s="8"/>
       <c r="C941" s="8"/>
@@ -17810,7 +17786,7 @@
       <c r="K941" s="7"/>
       <c r="L941" s="20"/>
     </row>
-    <row r="942" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A942" s="8"/>
       <c r="B942" s="8"/>
       <c r="C942" s="8"/>
@@ -17819,7 +17795,7 @@
       <c r="K942" s="7"/>
       <c r="L942" s="20"/>
     </row>
-    <row r="943" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A943" s="8"/>
       <c r="B943" s="8"/>
       <c r="C943" s="8"/>
@@ -17828,7 +17804,7 @@
       <c r="K943" s="7"/>
       <c r="L943" s="20"/>
     </row>
-    <row r="944" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="944" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A944" s="8"/>
       <c r="B944" s="8"/>
       <c r="C944" s="8"/>
@@ -17878,7 +17854,6 @@
       <c r="B949" s="8"/>
       <c r="C949" s="8"/>
       <c r="D949" s="8"/>
-      <c r="E949" s="3"/>
       <c r="K949" s="7"/>
       <c r="L949" s="20"/>
     </row>
@@ -17896,6 +17871,7 @@
       <c r="B951" s="8"/>
       <c r="C951" s="8"/>
       <c r="D951" s="8"/>
+      <c r="E951" s="3"/>
       <c r="K951" s="7"/>
       <c r="L951" s="20"/>
     </row>
@@ -17922,7 +17898,6 @@
       <c r="B954" s="8"/>
       <c r="C954" s="8"/>
       <c r="D954" s="8"/>
-      <c r="E954" s="3"/>
       <c r="K954" s="7"/>
       <c r="L954" s="20"/>
     </row>
@@ -17940,6 +17915,7 @@
       <c r="B956" s="8"/>
       <c r="C956" s="8"/>
       <c r="D956" s="8"/>
+      <c r="E956" s="3"/>
       <c r="K956" s="7"/>
       <c r="L956" s="20"/>
     </row>
@@ -17957,7 +17933,6 @@
       <c r="B958" s="8"/>
       <c r="C958" s="8"/>
       <c r="D958" s="8"/>
-      <c r="E958" s="3"/>
       <c r="K958" s="7"/>
       <c r="L958" s="20"/>
     </row>
@@ -17966,7 +17941,7 @@
       <c r="B959" s="8"/>
       <c r="C959" s="8"/>
       <c r="D959" s="8"/>
-      <c r="E959" s="3"/>
+      <c r="F959" s="8"/>
       <c r="K959" s="7"/>
       <c r="L959" s="20"/>
     </row>
@@ -17975,6 +17950,7 @@
       <c r="B960" s="8"/>
       <c r="C960" s="8"/>
       <c r="D960" s="8"/>
+      <c r="E960" s="3"/>
       <c r="K960" s="7"/>
       <c r="L960" s="20"/>
     </row>
@@ -17983,7 +17959,7 @@
       <c r="B961" s="8"/>
       <c r="C961" s="8"/>
       <c r="D961" s="8"/>
-      <c r="F961" s="8"/>
+      <c r="E961" s="3"/>
       <c r="K961" s="7"/>
       <c r="L961" s="20"/>
     </row>
@@ -18063,10 +18039,9 @@
       <c r="A970" s="8"/>
       <c r="B970" s="8"/>
       <c r="C970" s="8"/>
-      <c r="D970" s="8"/>
-      <c r="E970" s="3"/>
       <c r="K970" s="7"/>
       <c r="L970" s="20"/>
+      <c r="M970" s="8"/>
     </row>
     <row r="971" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A971" s="8"/>
@@ -18081,9 +18056,10 @@
       <c r="A972" s="8"/>
       <c r="B972" s="8"/>
       <c r="C972" s="8"/>
+      <c r="D972" s="8"/>
+      <c r="E972" s="3"/>
       <c r="K972" s="7"/>
       <c r="L972" s="20"/>
-      <c r="M972" s="8"/>
     </row>
     <row r="973" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A973" s="8"/>
@@ -18108,7 +18084,6 @@
       <c r="B975" s="8"/>
       <c r="C975" s="8"/>
       <c r="D975" s="8"/>
-      <c r="E975" s="3"/>
       <c r="K975" s="7"/>
       <c r="L975" s="20"/>
     </row>
@@ -18126,6 +18101,7 @@
       <c r="B977" s="8"/>
       <c r="C977" s="8"/>
       <c r="D977" s="8"/>
+      <c r="E977" s="3"/>
       <c r="K977" s="7"/>
       <c r="L977" s="20"/>
     </row>
@@ -18143,7 +18119,6 @@
       <c r="B979" s="8"/>
       <c r="C979" s="8"/>
       <c r="D979" s="8"/>
-      <c r="E979" s="3"/>
       <c r="K979" s="7"/>
       <c r="L979" s="20"/>
     </row>
@@ -18161,6 +18136,7 @@
       <c r="B981" s="8"/>
       <c r="C981" s="8"/>
       <c r="D981" s="8"/>
+      <c r="E981" s="3"/>
       <c r="K981" s="7"/>
       <c r="L981" s="20"/>
     </row>
@@ -18178,7 +18154,6 @@
       <c r="B983" s="8"/>
       <c r="C983" s="8"/>
       <c r="D983" s="8"/>
-      <c r="E983" s="3"/>
       <c r="K983" s="7"/>
       <c r="L983" s="20"/>
     </row>
@@ -18187,7 +18162,6 @@
       <c r="B984" s="8"/>
       <c r="C984" s="8"/>
       <c r="D984" s="8"/>
-      <c r="E984" s="3"/>
       <c r="K984" s="7"/>
       <c r="L984" s="20"/>
     </row>
@@ -18196,6 +18170,7 @@
       <c r="B985" s="8"/>
       <c r="C985" s="8"/>
       <c r="D985" s="8"/>
+      <c r="E985" s="3"/>
       <c r="K985" s="7"/>
       <c r="L985" s="20"/>
     </row>
@@ -18204,6 +18179,7 @@
       <c r="B986" s="8"/>
       <c r="C986" s="8"/>
       <c r="D986" s="8"/>
+      <c r="E986" s="3"/>
       <c r="K986" s="7"/>
       <c r="L986" s="20"/>
     </row>
@@ -18302,7 +18278,6 @@
       <c r="B997" s="8"/>
       <c r="C997" s="8"/>
       <c r="D997" s="8"/>
-      <c r="E997" s="3"/>
       <c r="K997" s="7"/>
       <c r="L997" s="20"/>
     </row>
@@ -18311,7 +18286,7 @@
       <c r="B998" s="8"/>
       <c r="C998" s="8"/>
       <c r="D998" s="8"/>
-      <c r="E998" s="3"/>
+      <c r="H998" s="8"/>
       <c r="K998" s="7"/>
       <c r="L998" s="20"/>
     </row>
@@ -18320,6 +18295,7 @@
       <c r="B999" s="8"/>
       <c r="C999" s="8"/>
       <c r="D999" s="8"/>
+      <c r="E999" s="3"/>
       <c r="K999" s="7"/>
       <c r="L999" s="20"/>
     </row>
@@ -18328,7 +18304,7 @@
       <c r="B1000" s="8"/>
       <c r="C1000" s="8"/>
       <c r="D1000" s="8"/>
-      <c r="H1000" s="8"/>
+      <c r="E1000" s="3"/>
       <c r="K1000" s="7"/>
       <c r="L1000" s="20"/>
     </row>
@@ -18337,7 +18313,6 @@
       <c r="B1001" s="8"/>
       <c r="C1001" s="8"/>
       <c r="D1001" s="8"/>
-      <c r="E1001" s="3"/>
       <c r="K1001" s="7"/>
       <c r="L1001" s="20"/>
     </row>
@@ -18355,6 +18330,7 @@
       <c r="B1003" s="8"/>
       <c r="C1003" s="8"/>
       <c r="D1003" s="8"/>
+      <c r="E1003" s="3"/>
       <c r="K1003" s="7"/>
       <c r="L1003" s="20"/>
     </row>
@@ -18435,7 +18411,6 @@
       <c r="B1012" s="8"/>
       <c r="C1012" s="8"/>
       <c r="D1012" s="8"/>
-      <c r="E1012" s="3"/>
       <c r="K1012" s="7"/>
       <c r="L1012" s="20"/>
     </row>
@@ -18470,6 +18445,7 @@
       <c r="B1016" s="8"/>
       <c r="C1016" s="8"/>
       <c r="D1016" s="8"/>
+      <c r="E1016" s="3"/>
       <c r="K1016" s="7"/>
       <c r="L1016" s="20"/>
     </row>
@@ -18487,7 +18463,6 @@
       <c r="B1018" s="8"/>
       <c r="C1018" s="8"/>
       <c r="D1018" s="8"/>
-      <c r="E1018" s="3"/>
       <c r="K1018" s="7"/>
       <c r="L1018" s="20"/>
     </row>
@@ -18496,53 +18471,37 @@
       <c r="B1019" s="8"/>
       <c r="C1019" s="8"/>
       <c r="D1019" s="8"/>
-      <c r="E1019" s="3"/>
       <c r="K1019" s="7"/>
       <c r="L1019" s="20"/>
     </row>
     <row r="1020" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1020" s="8"/>
-      <c r="B1020" s="8"/>
-      <c r="C1020" s="8"/>
-      <c r="D1020" s="8"/>
-      <c r="K1020" s="7"/>
-      <c r="L1020" s="20"/>
+      <c r="A1020" s="40"/>
+      <c r="B1020" s="40"/>
+      <c r="C1020" s="40"/>
+      <c r="D1020" s="40"/>
+      <c r="E1020" s="42"/>
+      <c r="F1020" s="40"/>
+      <c r="G1020" s="42"/>
+      <c r="H1020" s="42"/>
+      <c r="I1020" s="42"/>
+      <c r="J1020" s="42"/>
+      <c r="K1020" s="28"/>
+      <c r="L1020" s="24"/>
+      <c r="M1020" s="42"/>
     </row>
     <row r="1021" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1021" s="8"/>
       <c r="B1021" s="8"/>
       <c r="C1021" s="8"/>
       <c r="D1021" s="8"/>
+      <c r="E1021" s="3"/>
       <c r="K1021" s="7"/>
       <c r="L1021" s="20"/>
-    </row>
-    <row r="1022" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1022" s="40"/>
-      <c r="B1022" s="40"/>
-      <c r="C1022" s="40"/>
-      <c r="D1022" s="40"/>
-      <c r="E1022" s="42"/>
-      <c r="F1022" s="40"/>
-      <c r="G1022" s="42"/>
-      <c r="H1022" s="42"/>
-      <c r="I1022" s="42"/>
-      <c r="J1022" s="42"/>
-      <c r="K1022" s="28"/>
-      <c r="L1022" s="24"/>
-      <c r="M1022" s="42"/>
-    </row>
-    <row r="1023" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1023" s="8"/>
-      <c r="B1023" s="8"/>
-      <c r="C1023" s="8"/>
-      <c r="D1023" s="8"/>
-      <c r="E1023" s="3"/>
-      <c r="K1023" s="7"/>
-      <c r="L1023" s="20"/>
     </row>
   </sheetData>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/src/assets/docs/Schedule.xlsx
+++ b/src/assets/docs/Schedule.xlsx
@@ -8,18 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\workspace\nijisanji-schedule\src\assets\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F170725-4F2F-4307-ACA8-64998383E37B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEDF332E-42E8-4554-9FA1-029C0C90663B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7845" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ALL" sheetId="4" r:id="rId1"/>
-    <sheet name="ALL-orig" sheetId="1" r:id="rId2"/>
+    <sheet name="ALL-test" sheetId="4" r:id="rId1"/>
+    <sheet name="ALL" sheetId="1" r:id="rId2"/>
     <sheet name="TBD" sheetId="2" r:id="rId3"/>
     <sheet name="old" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ALL-orig'!$B$1:$B$292</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">ALL!$B$1:$B$292</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
